--- a/resources/progetti_ottobre_2025_finale.xlsx
+++ b/resources/progetti_ottobre_2025_finale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giacomoterreni/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giacomoterreni/projects/homestead7/citizen.test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40ACB0B2-E795-924B-883C-C345EE59D113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CDE606-D8A9-9D47-84C6-E61C5279D008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80420" yWindow="2360" windowWidth="19820" windowHeight="17640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="52900" yWindow="-840" windowWidth="46000" windowHeight="19920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Risposte del modulo 1" sheetId="1" r:id="rId1"/>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="237">
   <si>
     <t>Nr</t>
   </si>
@@ -898,6 +898,24 @@
   </si>
   <si>
     <t>Ricercatori; Pubblico generico; Appassionati</t>
+  </si>
+  <si>
+    <t>43.288000</t>
+  </si>
+  <si>
+    <t>43.303000</t>
+  </si>
+  <si>
+    <t>43.333000</t>
+  </si>
+  <si>
+    <t>11.320000</t>
+  </si>
+  <si>
+    <t>11.340000</t>
+  </si>
+  <si>
+    <t>11.350000</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1062,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1081,6 +1099,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1484,9 +1503,11 @@
     <col min="19" max="19" width="18.796875" customWidth="1"/>
     <col min="20" max="20" width="40.59765625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.19921875" customWidth="1"/>
-    <col min="22" max="22" width="16.796875" customWidth="1"/>
-    <col min="23" max="23" width="14" customWidth="1"/>
-    <col min="24" max="27" width="11.19921875" customWidth="1"/>
+    <col min="22" max="22" width="73.3984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="22.796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="11.19921875" customWidth="1"/>
     <col min="28" max="28" width="32.59765625" customWidth="1"/>
     <col min="29" max="29" width="11.19921875" customWidth="1"/>
     <col min="31" max="31" width="16.796875" bestFit="1" customWidth="1"/>
@@ -2606,8 +2627,12 @@
         <v>225</v>
       </c>
       <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
+      <c r="X15" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="Y15" s="26" t="s">
+        <v>234</v>
+      </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="16" t="s">
@@ -2680,8 +2705,12 @@
         <v>225</v>
       </c>
       <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
+      <c r="X16" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y16" s="26" t="s">
+        <v>235</v>
+      </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="16" t="s">
@@ -2754,8 +2783,12 @@
         <v>225</v>
       </c>
       <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
+      <c r="X17" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="Y17" s="26" t="s">
+        <v>236</v>
+      </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="16" t="s">

--- a/resources/progetti_ottobre_2025_finale.xlsx
+++ b/resources/progetti_ottobre_2025_finale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giacomoterreni/projects/homestead7/citizen.test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CDE606-D8A9-9D47-84C6-E61C5279D008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07996D4B-9DF9-9143-91EA-E13BA9416E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="52900" yWindow="-840" windowWidth="46000" windowHeight="19920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,10 +343,6 @@
 Tramite l'utilizzo dell'app, i partecipanti possono avere accesso alle mappe, segnalazioni e foto, fornendo così uno strumento prezioso per chi è interessato alla conservazione degli squali. Inoltre, l'app e i deliverable associati forniscono anche una serie di strumenti e manuali per l'identificazione delle specie e, per i pescatori, anche buone pratiche sulla manipolazione e liberazione degli animali. </t>
   </si>
   <si>
-    <t>Napoli
-Genova</t>
-  </si>
-  <si>
     <t>Napoli, Genova</t>
   </si>
   <si>
@@ -916,6 +912,9 @@
   </si>
   <si>
     <t>11.350000</t>
+  </si>
+  <si>
+    <t>Napoli;Genova</t>
   </si>
 </sst>
 </file>
@@ -1197,8 +1196,8 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>4724080</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>126720</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>25120</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1254,8 +1253,8 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>4724080</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>126720</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>25120</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1533,7 +1532,7 @@
         <v>6</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -1602,7 +1601,7 @@
         <v>27</v>
       </c>
       <c r="AE1" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1633,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>35</v>
@@ -1654,13 +1653,13 @@
         <v>39</v>
       </c>
       <c r="T2" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V2" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
@@ -1677,7 +1676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -1705,7 +1704,7 @@
         <v>45</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>46</v>
@@ -1728,13 +1727,13 @@
         <v>39</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
@@ -1751,7 +1750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>28</v>
       </c>
@@ -1779,7 +1778,7 @@
         <v>55</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L4" s="23" t="s">
         <v>56</v>
@@ -1802,13 +1801,13 @@
         <v>39</v>
       </c>
       <c r="T4" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V4" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
@@ -1825,7 +1824,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
@@ -1850,25 +1849,25 @@
         <v>65</v>
       </c>
       <c r="J5" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L5" s="23" t="s">
         <v>66</v>
-      </c>
-      <c r="K5" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L5" s="23" t="s">
-        <v>67</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>57</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="P5" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -1876,13 +1875,13 @@
         <v>39</v>
       </c>
       <c r="T5" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V5" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
@@ -1890,10 +1889,10 @@
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AC5" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AE5">
         <v>4</v>
@@ -1910,41 +1909,41 @@
         <v>46387</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>72</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="K6" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L6" s="25" t="s">
         <v>225</v>
-      </c>
-      <c r="L6" s="25" t="s">
-        <v>226</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>57</v>
       </c>
       <c r="N6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="O6" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="P6" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -1952,13 +1951,13 @@
         <v>39</v>
       </c>
       <c r="T6" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V6" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
@@ -1966,10 +1965,10 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC6" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE6">
         <v>5</v>
@@ -1986,41 +1985,41 @@
         <v>45991</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K7" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="N7" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="O7" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="P7" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
@@ -2028,13 +2027,13 @@
         <v>39</v>
       </c>
       <c r="T7" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V7" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
@@ -2042,16 +2041,16 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC7" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -2060,41 +2059,41 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="J8" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L8" s="24" t="s">
         <v>94</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L8" s="24" t="s">
-        <v>95</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>57</v>
       </c>
       <c r="N8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="O8" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="P8" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
@@ -2102,13 +2101,13 @@
         <v>39</v>
       </c>
       <c r="T8" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V8" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
@@ -2116,10 +2115,10 @@
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AC8" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AE8">
         <v>7</v>
@@ -2134,7 +2133,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="4" t="s">
@@ -2142,31 +2141,31 @@
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="K9" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L9" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>57</v>
       </c>
       <c r="N9" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="O9" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="P9" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -2174,13 +2173,13 @@
         <v>39</v>
       </c>
       <c r="T9" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V9" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
@@ -2188,10 +2187,10 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AC9" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AE9">
         <v>8</v>
@@ -2206,41 +2205,41 @@
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L10" s="25" t="s">
         <v>112</v>
-      </c>
-      <c r="K10" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L10" s="25" t="s">
-        <v>113</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>57</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O10" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="P10" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -2248,13 +2247,13 @@
         <v>39</v>
       </c>
       <c r="T10" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V10" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
@@ -2262,10 +2261,10 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AC10" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AE10">
         <v>9</v>
@@ -2280,41 +2279,41 @@
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L11" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="K11" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L11" s="23" t="s">
+      <c r="M11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N11" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N11" s="3" t="s">
+      <c r="O11" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="P11" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
@@ -2322,13 +2321,13 @@
         <v>39</v>
       </c>
       <c r="T11" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V11" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
@@ -2336,16 +2335,16 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AC11" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AE11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>28</v>
       </c>
@@ -2354,41 +2353,41 @@
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="F12" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>130</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="J12" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L12" s="12" t="s">
         <v>132</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="K12" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>133</v>
       </c>
       <c r="M12" s="12" t="s">
         <v>57</v>
       </c>
       <c r="N12" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="O12" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="O12" s="13" t="s">
+      <c r="P12" s="12" t="s">
         <v>135</v>
-      </c>
-      <c r="P12" s="12" t="s">
-        <v>136</v>
       </c>
       <c r="Q12" s="12"/>
       <c r="R12" s="12"/>
@@ -2396,13 +2395,13 @@
         <v>39</v>
       </c>
       <c r="T12" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V12" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W12" s="12"/>
       <c r="X12" s="12"/>
@@ -2410,10 +2409,10 @@
       <c r="Z12" s="12"/>
       <c r="AA12" s="12"/>
       <c r="AB12" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC12" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AE12">
         <v>11</v>
@@ -2428,41 +2427,41 @@
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L13" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="K13" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L13" s="23" t="s">
+      <c r="M13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N13" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="M13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N13" s="3" t="s">
+      <c r="O13" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="P13" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
@@ -2470,13 +2469,13 @@
         <v>39</v>
       </c>
       <c r="T13" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V13" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
@@ -2484,10 +2483,10 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AC13" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AE13">
         <v>12</v>
@@ -2502,41 +2501,41 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>148</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>149</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="J14" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L14" s="23" t="s">
         <v>152</v>
-      </c>
-      <c r="K14" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L14" s="23" t="s">
-        <v>153</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>57</v>
       </c>
       <c r="N14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="O14" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="P14" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
@@ -2544,13 +2543,13 @@
         <v>39</v>
       </c>
       <c r="T14" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V14" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
@@ -2558,10 +2557,10 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AC14" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AE14">
         <v>13</v>
@@ -2576,41 +2575,41 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="J15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L15" s="25" t="s">
         <v>161</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="K15" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L15" s="25" t="s">
-        <v>162</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>57</v>
       </c>
       <c r="N15" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="O15" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="P15" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
@@ -2618,28 +2617,28 @@
         <v>39</v>
       </c>
       <c r="T15" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V15" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W15" s="3"/>
       <c r="X15" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Y15" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC15" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AE15">
         <v>14</v>
@@ -2654,41 +2653,41 @@
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="J16" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L16" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="K16" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L16" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>57</v>
       </c>
       <c r="N16" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="O16" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="P16" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -2696,28 +2695,28 @@
         <v>39</v>
       </c>
       <c r="T16" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V16" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W16" s="3"/>
       <c r="X16" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Y16" s="26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC16" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AE16">
         <v>15</v>
@@ -2732,41 +2731,41 @@
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="J17" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L17" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N17" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="K17" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L17" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N17" s="3" t="s">
+      <c r="O17" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="O17" s="4" t="s">
+      <c r="P17" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -2774,28 +2773,28 @@
         <v>39</v>
       </c>
       <c r="T17" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V17" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W17" s="3"/>
       <c r="X17" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Y17" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC17" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AE17">
         <v>16</v>
@@ -2810,41 +2809,41 @@
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L18" s="23" t="s">
         <v>186</v>
-      </c>
-      <c r="K18" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L18" s="23" t="s">
-        <v>187</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>57</v>
       </c>
       <c r="N18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
@@ -2852,13 +2851,13 @@
         <v>39</v>
       </c>
       <c r="T18" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V18" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
@@ -2866,10 +2865,10 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AC18" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AE18">
         <v>17</v>
@@ -2884,41 +2883,41 @@
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>191</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>192</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="J19" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="M19" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="J19" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="K19" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="M19" s="4" t="s">
+      <c r="N19" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="O19" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="N19" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="O19" s="19" t="s">
+      <c r="P19" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
@@ -2926,13 +2925,13 @@
         <v>39</v>
       </c>
       <c r="T19" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V19" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
@@ -2940,10 +2939,10 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AC19" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AE19">
         <v>18</v>
@@ -4009,7 +4008,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>7</v>
@@ -4084,57 +4083,57 @@
       </c>
       <c r="H2" s="1"/>
       <c r="K2" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="X2" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="X2" s="20" t="s">
+      <c r="Y2" s="20" t="s">
         <v>207</v>
-      </c>
-      <c r="Y2" s="20" t="s">
-        <v>208</v>
       </c>
       <c r="AA2" s="20"/>
       <c r="AB2" s="20"/>
     </row>
     <row r="3" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="H3" s="1"/>
       <c r="M3" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="X3" s="20"/>
       <c r="Y3" s="20"/>
@@ -4143,17 +4142,17 @@
     </row>
     <row r="4" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G4" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H4" s="1"/>
       <c r="M4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="T4" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="X4" s="20"/>
       <c r="Y4" s="20"/>
@@ -4162,17 +4161,17 @@
     </row>
     <row r="5" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G5" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="1"/>
       <c r="M5" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="T5" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="X5" s="20"/>
       <c r="Y5" s="20"/>
@@ -4181,7 +4180,7 @@
     </row>
     <row r="6" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="T6" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X6" s="20"/>
       <c r="Y6" s="20"/>

--- a/resources/progetti_ottobre_2025_finale.xlsx
+++ b/resources/progetti_ottobre_2025_finale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giacomoterreni/projects/homestead7/citizen.test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07996D4B-9DF9-9143-91EA-E13BA9416E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21731F33-4EDF-414B-B43C-CC917B1FE4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="52900" yWindow="-840" windowWidth="46000" windowHeight="19920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="239">
   <si>
     <t>Nr</t>
   </si>
@@ -915,6 +915,12 @@
   </si>
   <si>
     <t>Napoli;Genova</t>
+  </si>
+  <si>
+    <t>44.910600</t>
+  </si>
+  <si>
+    <t>8.610900</t>
   </si>
 </sst>
 </file>
@@ -1061,7 +1067,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1099,6 +1105,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2110,8 +2117,8 @@
         <v>224</v>
       </c>
       <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
+      <c r="X8" s="26"/>
+      <c r="Y8" s="26"/>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="8" t="s">
@@ -2182,8 +2189,8 @@
         <v>224</v>
       </c>
       <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
+      <c r="X9" s="26"/>
+      <c r="Y9" s="26"/>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="8" t="s">
@@ -2256,8 +2263,8 @@
         <v>224</v>
       </c>
       <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
+      <c r="X10" s="26"/>
+      <c r="Y10" s="26"/>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="8" t="s">
@@ -2330,8 +2337,8 @@
         <v>224</v>
       </c>
       <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
+      <c r="X11" s="26"/>
+      <c r="Y11" s="26"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="8" t="s">
@@ -2404,8 +2411,8 @@
         <v>224</v>
       </c>
       <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="12"/>
+      <c r="X12" s="27"/>
+      <c r="Y12" s="27"/>
       <c r="Z12" s="12"/>
       <c r="AA12" s="12"/>
       <c r="AB12" s="15" t="s">
@@ -2478,8 +2485,8 @@
         <v>224</v>
       </c>
       <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
+      <c r="X13" s="26"/>
+      <c r="Y13" s="26"/>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="16" t="s">
@@ -2552,8 +2559,8 @@
         <v>224</v>
       </c>
       <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
+      <c r="X14" s="26"/>
+      <c r="Y14" s="26"/>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="16" t="s">
@@ -2860,8 +2867,8 @@
         <v>224</v>
       </c>
       <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
+      <c r="X18" s="26"/>
+      <c r="Y18" s="26"/>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="8" t="s">
@@ -2934,8 +2941,12 @@
         <v>224</v>
       </c>
       <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
+      <c r="X19" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y19" s="26" t="s">
+        <v>238</v>
+      </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="16" t="s">

--- a/resources/progetti_ottobre_2025_finale.xlsx
+++ b/resources/progetti_ottobre_2025_finale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giacomoterreni/projects/homestead7/citizen.test/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giacomoterreni/projects/homestead7/citizen/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21731F33-4EDF-414B-B43C-CC917B1FE4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3A9377-EDF6-9C47-8890-6ABF2C651954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52900" yWindow="-840" windowWidth="46000" windowHeight="19920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8840" yWindow="3080" windowWidth="46000" windowHeight="19920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Risposte del modulo 1" sheetId="1" r:id="rId1"/>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="258">
   <si>
     <t>Nr</t>
   </si>
@@ -922,6 +922,90 @@
   <si>
     <t>8.610900</t>
   </si>
+  <si>
+    <t>Il progetto Wikiplantbase #Sardegna - verso un catalogo collaborativo, online e gratuito delle piante vascolari della Sardegna, intende facilitare la raccolta e la consultazione di dati floristici per la Sardegna, con un'interfaccia liberamente accessibile ed aperta al contributo di tutti. E' possibile inserire segnalazioni tratte da campioni d'erbario, libri, articoli pubblicati su riviste scientifiche e osservazioni personali. Le segnalazioni georeferenziate sono cartografate sulle mappe Google.</t>
+  </si>
+  <si>
+    <t>Neptis è un progetto di ricerca per aumentare in modo sostanziale le attuali conoscenze sulla distribuzione, ecologia e stato di conservazione delle specie di farfalle (Lepidotteri Papilionoidei) che vivono nelle aree collinari e montane dell’Italia nord-orientale.
+ È un progetto di “citizen science”, ossia si basa sulla collaborazione volontaria di chiunque voglia contribuire, condividendo le proprie osservazioni di farfalle sul territorio.
+ Il progetto durerà 3 anni. È coordinato da Lucio Bonato, assieme a Enrico Carta, Luca Gregnanin ed Enrico Vettorazzo. È promosso dal Dipartimento di Biologia dell’Università di Padova e dal Parco Nazionale Dolomiti Bellunesi.</t>
+  </si>
+  <si>
+    <t>Il progetto si propone di studiare e monitorare la presenza e la diffusione di specie rare, termofile o aliene nei mari italiani e, più in generale, nel Mediterraneo, con particolare attenzione (ma non esclusivamente) alle specie ittiche.
+ L’attività si fonda su un approccio di citizen science, che coinvolge subacquei, pescatori e altre persone legate al mare. I collaboratori vengono contattati attraverso reti personali oppure tramite social network, in particolare Facebook, dove spesso gli utenti condividono osservazioni e chiedono supporto per l’identificazione di pesci o altri organismi. Alcune di queste segnalazioni si rivelano di grande interesse scientifico, in quanto riguardano specie poco comuni o scarsamente documentate nel Mediterraneo.
+ Grazie alla partecipazione crescente della comunità, è stato possibile costruire una rete di segnalazioni tempestive che non solo arricchiscono il monitoraggio scientifico, ma offrono anche un supporto diretto agli osservatori attraverso processi di identificazione accurati.
+ I dati raccolti vengono impiegati per la produzione di pubblicazioni scientifiche, con un riconoscimento formale dei contributi ricevuti dai collaboratori. Inoltre, il progetto integra oggi tecniche molecolari alle osservazioni di citizen science, al fine di rafforzare la solidità e l’affidabilità dei risultati ottenuti.</t>
+  </si>
+  <si>
+    <t>Il progetto si concentra sull’identificazione e la mappatura delle segnalazioni di squali nelle acque italiane, con l’obiettivo di aumentare la conoscenza scientifica e la consapevolezza pubblica sulla distribuzione di questi animali nel Mediterraneo.
+ I cittadini possono contribuire attivamente inviando segnalazioni fotografiche e contestualizzate di avvistamenti di squali, sia in mare aperto (diporto, immersioni, crociere) sia lungo le coste (ad esempio nei mercati ittici). Tutte le segnalazioni vengono verificate e catalogate dagli esperti della Stazione Zoologica Anton Dohrn (SZN), contribuendo alla creazione di una mappa interattiva – disponibile tramite app – della distribuzione delle specie di squali presenti nel Mediterraneo italiano.
+ Questo approccio partecipativo è fondamentale: senza il coinvolgimento diretto di pescatori, subacquei e appassionati del mare, tali mappature risulterebbero estremamente difficili, se non impossibili. I dati raccolti non solo arricchiscono la conoscenza scientifica, ma forniscono anche strumenti utili per la conservazione dei condroitti, categoria che include specie spesso minacciate e vulnerabili al bycatch.
+ Il progetto non si limita alla raccolta di segnalazioni: tramite l’app, i partecipanti hanno accesso a mappe, fotografie, guide di identificazione delle specie e manuali con buone pratiche di pesca sostenibile, comprese tecniche per la corretta manipolazione e liberazione degli animali catturati accidentalmente.</t>
+  </si>
+  <si>
+    <t>L’app BOB (acronimo di Behavioural Observations in Beetles), un’iniziativa del CREA, è dedicata a contribuire allo studio del comportamento degli insetti protetti in Europa. I cittadini scienziati sono invitati a osservare tre particolari specie di coleotteri presenti nei loro dintorni: il cervo volante (Lucanus cervus), la rosalia alpina (Rosalia alpina) e il morimo (Morimus asper).
+ Queste tre specie di coleotteri sono tutte protette dalla Direttiva Habitat dell’Unione Europea. Durante la fase larvale, esse dipendono dal legno morto come risorsa fondamentale per il loro sviluppo, motivo per cui sono definite “saproxiliche”. Quando i cittadini scienziati incontrano uno di questi coleotteri, possono osservarlo, scattare una foto e caricarla sull’app BOB insieme ad alcune informazioni richieste. Se i partecipanti hanno difficoltà a identificare con precisione la specie osservata, possono comunque caricare le foto con una descrizione: il team del CREA sarà in grado di lavorare con le informazioni fornite.</t>
+  </si>
+  <si>
+    <t>Obiettivo del progetto Life ESC 360 è quello di offrire ai giovani la possibilità di fare esperienza nella conservazione della natura attraverso attività di monitoraggio di specie protette all’interno di Riserve Statali in Italia; fondamentale per una gestione mirata delle stesse. I dati raccolti dai volontari, rappresentano un incremento di conoscenza sulla presenza e sull’andamento delle popolazioni di specie di interesse comunitario, anche per le finalità del rapporto tecnico previsto dall’articolo 17 della Direttiva Habitat sul loro stato di conservazione. I volontari opportunatamente formati, applicheranno protocolli standard per il monitoraggio di numerose specie di invertebrati, anfibi, uccelli, mammiferi di interesse comunitario specie e habitat di in prevalenza forestali.</t>
+  </si>
+  <si>
+    <t>Guardiani della Costa è un progetto educativo che si inserisce all’interno del percorso didattico delle scuole superiori rivolto a studenti e docenti di tutti gli istituti scolastici d’Italia.
+ Lo definiamo un progetto di citizen science, ovvero di scienza applicata collettivamente da cittadini e cittadine informati e responsabili. Vivere quest’esperienza è semplice: con una serie di strumenti gratuiti gli studenti potranno aumentare la loro consapevolezza sull’unicità del patrimonio naturalistico delle coste italiane, sui problemi che derivano dall’inquinamento marino, in particolare dall’aumento dei rifiuti marini lungo le coste.</t>
+  </si>
+  <si>
+    <t>Il progetto SOS Pinna: la subacquea aiuta la Ricerca è uno strumento per la salvaguardia di Pinna nobilis, specie iconica del Mediterraneo a rischio di estinzione</t>
+  </si>
+  <si>
+    <t>Il Butterfly Monitoring Scheme (o rete di monitoraggio delle farfalle) consiste nel conteggio delle specie di farfalle seguendo un metodo condiviso in tutta Europa. Il progetto ha lo scopo di valutare l’abbondanza delle popolazioni di farfalle, al fine di stabilire strategie di conservazione appropriate, grazie all’impegno di moltissimi volontari.
+ Se ti piacciono le farfalle e le camminate all’aria aperte entra anche tu a far parte del ITBMS, condividi la passione per questi meravigliosi insetti con tutta Europa, diventando un cittadino scienziato.</t>
+  </si>
+  <si>
+    <t>Il progetto ha come obiettivo lo sviluppo di un framework per la gestione e il monitoraggio della biodiversità negli agroecosistemi europei, promuovendo il coinvolgimento attivo sia degli agricoltori sia della cittadinanza. L’approccio si fonda sulla collaborazione tra comunità locali ed esperti, con l’intento di raccogliere dati scientifici e aumentare la consapevolezza sull’importanza della biodiversità nelle aree agricole.
+ Una parte centrale del progetto è rappresentata dall’organizzazione di BioBlitz nelle aree di studio, eventi che permettono alla popolazione di partecipare direttamente all’osservazione e identificazione delle specie presenti. Nel 2023 sono stati organizzati due BioBlitz:
+ il primo incluso nel City Nature Challenge, con il patrocinio del NBFC;
+ il secondo in collaborazione con il Museo di Storia Naturale e lo Sportello di Agroecologia di Calci.
+ Durante i BioBlitz, esperti di flora, avifauna, entomofauna, rettili e anfibi hanno guidato i partecipanti in piccoli gruppi, fornendo supporto nell’identificazione degli organismi osservati e fotografati. Per il City Nature Challenge è stato suggerito l’utilizzo della piattaforma iNaturalist per registrare le osservazioni, così da contribuire alla raccolta di dati condivisi a livello globale.</t>
+  </si>
+  <si>
+    <t>L’individuazione precoce delle specie aliene invasive e la possibilità di tracciare la loro diffusione sono aspetti fondamentali per prendere decisioni efficaci di gestione e contenimento. La citizen science rappresenta uno strumento prezioso per raccogliere rapidamente informazioni sulla biodiversità e sulla distribuzione delle specie.
+ La cimice asiatica marrone marmorizzata (Halyomorpha halys) è un insetto invasivo altamente dannoso per le colture agricole e considerato anche una fastidiosa presenza nelle abitazioni. In Italia è stata segnalata per la prima volta nel 2012 in Emilia-Romagna, una delle principali regioni frutticole d’Europa.
+ Per ottenere rapidamente dati sulla sua distribuzione nelle aree invase, è stata avviata un’indagine che ha combinato attività di citizen science e ricerche dirette, anche attraverso l’uso di canali multimediali. Sono stati raccolti dati relativi a quando, dove e come l’insetto è stato osservato, insieme a fotografie e campioni.</t>
+  </si>
+  <si>
+    <t>CS4RIVERS è un progetto di citizen science condotto dall’unità scientifica dell’Università di Siena responsabile dello Spoke 3 del National Biodiversity Future Center, un progetto finanziato dal PNRR che aggrega la ricerca scientifica nazionale di eccellenza e le moderne tecnologie per monitorare, preservare e ripristinare la biodiversità italiana e mediterranea al fine di contrastare l’impatto antropico, gli effetti dei cambiamenti climatici e di supportare i servizi ecosistemici in chiave sostenibile.</t>
+  </si>
+  <si>
+    <t>Il monitoraggio della biodiversità è uno strumento fondamentale per valutare lo stato di salute dell’ambiente, ma le istituzioni spesso non dispongono di risorse economiche e di personale sufficienti per condurre campagne su larga scala. Per questo motivo è nato il DUEproject – Divers United for the Environment, un programma dedicato al monitoraggio della biodiversità del Mar Mediterraneo con il contributo diretto dei cittadini.
+ Il progetto è stato ideato da un gruppo di ricercatori dell’Università di Bologna, con l’obiettivo di proteggere la fragile vita marina mediterranea attraverso il coinvolgimento della comunità dei subacquei ricreativi.
+ La nostra missione è:
+ Coinvolgere migliaia di subacquei nella raccolta di dati sulla presenza e abbondanza delle principali specie mediterranee;
+ Accrescere la conoscenza e la consapevolezza ambientale;
+ Stimolare le autorità locali a migliorare la gestione delle risorse marine.
+ Attraverso il DUEproject, la citizen science e la passione dei subacquei diventano strumenti concreti per la tutela del Mediterraneo e delle sue preziose risorse naturali.</t>
+  </si>
+  <si>
+    <t>Si tratta di un progetto di citizen science di monitoraggio a scala nazionale di molluschi terrestri in ambiente urbano, promosso dal Museo di Storia Naturale Accademia dei Fisiocritici. Le nostre città ospitano habitat ricchi e diversificati, ma la biodiversità urbana è un campo ancora abbastanza inesplorato: chiocciole e lumache sono ottimi indicatori di qualità ambientale, soprattutto a livello urbano, poiché svolgono un ruolo cruciale nella generazione del suolo e nel riciclo dei nutrienti. Obiettivo del monitoraggio è anche capire gli effetti dei cambiamenti climatici o quali meccanismi causino l’arrivo di specie aliene.ù</t>
+  </si>
+  <si>
+    <t>Progetto di monitoraggio a scala nazionale degli organismi animali (invertebrati e vertebrati) che vivono nelle nostre abitazioni, promosso dal Museo di Storia Naturale Accademia dei Fisiocritici (Siena).
+ In ogni casa, condividiamo la vita quotidiana con centinaia di migliaia di altri esseri viventi alcuni invisibili, altri inaspettati, di aspetto bizzarro, spesso ospiti innocui delle nostre abitazioni.</t>
+  </si>
+  <si>
+    <t>Siena BiodiverCity è un progetto di scienza partecipata del Museo di Storia Naturale Accademia Fisiocritici che ha lo scopo di censire la biodiversità urbana di Siena: scopri e osserva le specie di animali, funghi e piante presenti nel territorio del Comune di Siena e caricale su iNaturalist!</t>
+  </si>
+  <si>
+    <t>È sempre più difficile osservare individui ancora vivi di Pinna nobilis, il più grande bivalve endemico del Mar Mediterraneo. Questa specie, ritenuta oggi in “pericolo critico” e inserita nella lista rossa IUCN, è minacciata da una malattia, causata dall’azione congiunta di microrganismi, tra cui protozoi e batteri, che negli ultimi anni ha determinato una mortalità senza precedenti di P. nobilis, riducendone drasticamente la popolazione a scala di bacino Mediterraneo. Il progetto LIFE Pinna intende contrastare questo fenomeno per salvaguardare la specie dall’estinzione.
+ Il ritrovamento di individui superstiti di Pinna nobilis ancora in salute è essenziale per proteggerli e per studiare le loro capacità di adattamento a livello genetico ed ecologico. Per riuscire in questa impresa è necessario l’aiuto di tutti: non solo degli scienziati, ma anche di subacquei, diportisti e di chiunque ami il mare e la sua biodiversità. Questi grandi molluschi sono ormai rari lungo le nostre coste e ogni segnalazione di individui vivi è preziosa e contribuisce ad aumentare le possibilità di sopravvivenza della specie.
+ Le segnalazioni da voi inserite saranno verificate dagli scienziati di LIFE Pinna e per quelle che si riveleranno più significative saranno previsti premi sotto forma di libri, gadgets e la possibilità di visitare i laboratori di ricerca coinvolti del progetto. È quindi una vera caccia al tesoro.</t>
+  </si>
+  <si>
+    <t>CollembolIce è un progetto di ricerca partecipata (citizen science, ovvero ricerca scientifica cui partecipano attivamente i cittadini e cittadine, in questo caso professioniste e professionisti della montagna e dei ghiacciai), che mira a raccogliere dati sulla biodiversità e sulla distribuzione dei collemboli supraglaciali alpini, le celebri “pulci dei ghiacciai”, e a coinvolgere e sensibilizzare chi frequenta l’alta quota nello studio e il monitoraggio di organismi glaciali.
+ La biodiversità delle pulci dei ghiacciai è estremamente specializzata e rara, ancora poco nota a livello globale. Nonostante questo, è già fortemente minacciata di scomparsa dal riscaldamento globale e dall’estinzione dei ghiacciai.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Università degli Studi di Sassari </t>
+  </si>
 </sst>
 </file>
 
@@ -931,7 +1015,7 @@
     <numFmt numFmtId="164" formatCode="[$-410]dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1028,6 +1112,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1067,7 +1167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1106,6 +1206,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1486,8 +1589,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE997"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AD997"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.19921875" customWidth="1"/>
     <col min="2" max="2" width="15.796875" customWidth="1"/>
@@ -1509,17 +1612,16 @@
     <col min="19" max="19" width="18.796875" customWidth="1"/>
     <col min="20" max="20" width="40.59765625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.19921875" customWidth="1"/>
-    <col min="22" max="22" width="73.3984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="22.796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="11.19921875" customWidth="1"/>
-    <col min="28" max="28" width="32.59765625" customWidth="1"/>
-    <col min="29" max="29" width="11.19921875" customWidth="1"/>
-    <col min="31" max="31" width="16.796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="11.19921875" customWidth="1"/>
+    <col min="27" max="27" width="32.59765625" customWidth="1"/>
+    <col min="28" max="28" width="11.19921875" customWidth="1"/>
+    <col min="30" max="30" width="16.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1584,34 +1686,31 @@
         <v>19</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="22" t="s">
+      <c r="AD1" s="22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
@@ -1628,7 +1727,9 @@
       <c r="F2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="28" t="s">
+        <v>239</v>
+      </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
       </c>
@@ -1647,7 +1748,9 @@
       <c r="M2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="3"/>
+      <c r="N2" s="29" t="s">
+        <v>257</v>
+      </c>
       <c r="O2" s="4" t="s">
         <v>37</v>
       </c>
@@ -1665,25 +1768,22 @@
       <c r="U2" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V2" s="21" t="s">
-        <v>224</v>
-      </c>
+      <c r="V2" s="3"/>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
+      <c r="AA2" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="AB2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="AC2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE2">
+      <c r="AD2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="25" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -1700,7 +1800,9 @@
       <c r="F3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="29" t="s">
+        <v>240</v>
+      </c>
       <c r="H3" s="3" t="s">
         <v>43</v>
       </c>
@@ -1739,25 +1841,22 @@
       <c r="U3" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V3" s="21" t="s">
-        <v>224</v>
-      </c>
+      <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
+      <c r="AA3" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="AB3" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="AC3" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE3">
+      <c r="AD3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="16" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>28</v>
       </c>
@@ -1774,7 +1873,9 @@
       <c r="F4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="4"/>
+      <c r="G4" s="29" t="s">
+        <v>241</v>
+      </c>
       <c r="H4" s="3" t="s">
         <v>53</v>
       </c>
@@ -1813,25 +1914,22 @@
       <c r="U4" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V4" s="21" t="s">
-        <v>224</v>
-      </c>
+      <c r="V4" s="3"/>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
+      <c r="AA4" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="AB4" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="AC4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE4">
+      <c r="AD4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="20" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
@@ -1848,7 +1946,9 @@
       <c r="F5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="30" t="s">
+        <v>242</v>
+      </c>
       <c r="H5" s="3" t="s">
         <v>64</v>
       </c>
@@ -1887,25 +1987,22 @@
       <c r="U5" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V5" s="21" t="s">
-        <v>224</v>
-      </c>
+      <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
+      <c r="AA5" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="AB5" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="AC5" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE5">
+      <c r="AD5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>28</v>
       </c>
@@ -1924,7 +2021,9 @@
       <c r="F6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="4"/>
+      <c r="G6" s="29" t="s">
+        <v>243</v>
+      </c>
       <c r="H6" s="3" t="s">
         <v>73</v>
       </c>
@@ -1963,25 +2062,22 @@
       <c r="U6" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V6" s="21" t="s">
-        <v>224</v>
-      </c>
+      <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
+      <c r="AA6" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB6" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="AC6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE6">
+      <c r="AD6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
@@ -2000,7 +2096,9 @@
       <c r="F7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="4"/>
+      <c r="G7" s="29" t="s">
+        <v>244</v>
+      </c>
       <c r="H7" s="3" t="s">
         <v>82</v>
       </c>
@@ -2039,25 +2137,22 @@
       <c r="U7" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V7" s="21" t="s">
-        <v>224</v>
-      </c>
+      <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
+      <c r="AA7" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="AB7" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AC7" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE7">
+      <c r="AD7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="18" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -2074,7 +2169,9 @@
       <c r="F8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="4"/>
+      <c r="G8" s="29" t="s">
+        <v>245</v>
+      </c>
       <c r="H8" s="3" t="s">
         <v>92</v>
       </c>
@@ -2113,25 +2210,22 @@
       <c r="U8" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V8" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="26"/>
       <c r="X8" s="26"/>
-      <c r="Y8" s="26"/>
+      <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
+      <c r="AA8" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="AB8" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="AC8" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE8">
+      <c r="AD8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>28</v>
       </c>
@@ -2146,7 +2240,9 @@
       <c r="F9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="4"/>
+      <c r="G9" s="29" t="s">
+        <v>246</v>
+      </c>
       <c r="H9" s="3" t="s">
         <v>100</v>
       </c>
@@ -2185,25 +2281,22 @@
       <c r="U9" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V9" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="26"/>
       <c r="X9" s="26"/>
-      <c r="Y9" s="26"/>
+      <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
+      <c r="AA9" s="8" t="s">
+        <v>106</v>
+      </c>
       <c r="AB9" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="AC9" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="AE9">
+      <c r="AD9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
@@ -2220,7 +2313,9 @@
       <c r="F10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="4"/>
+      <c r="G10" s="29" t="s">
+        <v>247</v>
+      </c>
       <c r="H10" s="3" t="s">
         <v>109</v>
       </c>
@@ -2259,25 +2354,22 @@
       <c r="U10" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V10" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="26"/>
       <c r="X10" s="26"/>
-      <c r="Y10" s="26"/>
+      <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
+      <c r="AA10" s="8" t="s">
+        <v>116</v>
+      </c>
       <c r="AB10" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="AC10" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE10">
+      <c r="AD10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>28</v>
       </c>
@@ -2294,7 +2386,9 @@
       <c r="F11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="4"/>
+      <c r="G11" s="29" t="s">
+        <v>248</v>
+      </c>
       <c r="H11" s="3" t="s">
         <v>119</v>
       </c>
@@ -2333,25 +2427,22 @@
       <c r="U11" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V11" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="26"/>
       <c r="X11" s="26"/>
-      <c r="Y11" s="26"/>
+      <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
+      <c r="AA11" s="8" t="s">
+        <v>126</v>
+      </c>
       <c r="AB11" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="AC11" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="AE11">
+      <c r="AD11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="19" customHeight="1">
       <c r="A12" s="13" t="s">
         <v>28</v>
       </c>
@@ -2368,7 +2459,9 @@
       <c r="F12" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G12" s="12"/>
+      <c r="G12" s="28" t="s">
+        <v>249</v>
+      </c>
       <c r="H12" s="12" t="s">
         <v>130</v>
       </c>
@@ -2407,25 +2500,22 @@
       <c r="U12" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V12" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W12" s="12"/>
+      <c r="V12" s="12"/>
+      <c r="W12" s="27"/>
       <c r="X12" s="27"/>
-      <c r="Y12" s="27"/>
+      <c r="Y12" s="12"/>
       <c r="Z12" s="12"/>
-      <c r="AA12" s="12"/>
+      <c r="AA12" s="15" t="s">
+        <v>136</v>
+      </c>
       <c r="AB12" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="AC12" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE12">
+      <c r="AD12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>28</v>
       </c>
@@ -2442,7 +2532,9 @@
       <c r="F13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="4"/>
+      <c r="G13" s="29" t="s">
+        <v>250</v>
+      </c>
       <c r="H13" s="3" t="s">
         <v>139</v>
       </c>
@@ -2481,25 +2573,22 @@
       <c r="U13" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V13" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="26"/>
       <c r="X13" s="26"/>
-      <c r="Y13" s="26"/>
+      <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
+      <c r="AA13" s="16" t="s">
+        <v>146</v>
+      </c>
       <c r="AB13" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="AC13" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="AE13">
+      <c r="AD13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>28</v>
       </c>
@@ -2516,7 +2605,9 @@
       <c r="F14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="4"/>
+      <c r="G14" s="29" t="s">
+        <v>251</v>
+      </c>
       <c r="H14" s="3" t="s">
         <v>149</v>
       </c>
@@ -2555,25 +2646,22 @@
       <c r="U14" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V14" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="26"/>
       <c r="X14" s="26"/>
-      <c r="Y14" s="26"/>
+      <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
+      <c r="AA14" s="16" t="s">
+        <v>156</v>
+      </c>
       <c r="AB14" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="AC14" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE14">
+      <c r="AD14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
@@ -2590,7 +2678,9 @@
       <c r="F15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="4"/>
+      <c r="G15" s="29" t="s">
+        <v>252</v>
+      </c>
       <c r="H15" s="3" t="s">
         <v>159</v>
       </c>
@@ -2629,29 +2719,26 @@
       <c r="U15" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V15" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="26" t="s">
+        <v>230</v>
+      </c>
       <c r="X15" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="Y15" s="26" t="s">
         <v>233</v>
       </c>
+      <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
+      <c r="AA15" s="16" t="s">
+        <v>165</v>
+      </c>
       <c r="AB15" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AC15" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="AE15">
+      <c r="AD15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
@@ -2668,7 +2755,9 @@
       <c r="F16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="4"/>
+      <c r="G16" s="29" t="s">
+        <v>253</v>
+      </c>
       <c r="H16" s="3" t="s">
         <v>168</v>
       </c>
@@ -2707,29 +2796,26 @@
       <c r="U16" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V16" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="26" t="s">
+        <v>231</v>
+      </c>
       <c r="X16" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="Y16" s="26" t="s">
         <v>234</v>
       </c>
+      <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
+      <c r="AA16" s="16" t="s">
+        <v>165</v>
+      </c>
       <c r="AB16" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AC16" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="AE16">
+      <c r="AD16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -2746,7 +2832,9 @@
       <c r="F17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="4"/>
+      <c r="G17" s="29" t="s">
+        <v>254</v>
+      </c>
       <c r="H17" s="7" t="s">
         <v>176</v>
       </c>
@@ -2785,29 +2873,26 @@
       <c r="U17" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V17" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="26" t="s">
+        <v>232</v>
+      </c>
       <c r="X17" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="Y17" s="26" t="s">
         <v>235</v>
       </c>
+      <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
+      <c r="AA17" s="16" t="s">
+        <v>165</v>
+      </c>
       <c r="AB17" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="AC17" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="AE17">
+      <c r="AD17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>28</v>
       </c>
@@ -2824,7 +2909,9 @@
       <c r="F18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="4"/>
+      <c r="G18" s="29" t="s">
+        <v>255</v>
+      </c>
       <c r="H18" s="3" t="s">
         <v>183</v>
       </c>
@@ -2863,25 +2950,22 @@
       <c r="U18" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V18" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="26"/>
       <c r="X18" s="26"/>
-      <c r="Y18" s="26"/>
+      <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
+      <c r="AA18" s="8" t="s">
+        <v>189</v>
+      </c>
       <c r="AB18" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="AC18" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="AE18">
+      <c r="AD18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" ht="15.75" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>28</v>
       </c>
@@ -2898,7 +2982,9 @@
       <c r="F19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G19" s="4"/>
+      <c r="G19" s="29" t="s">
+        <v>256</v>
+      </c>
       <c r="H19" s="4" t="s">
         <v>192</v>
       </c>
@@ -2937,1017 +3023,1014 @@
       <c r="U19" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="V19" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="W19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="26" t="s">
+        <v>237</v>
+      </c>
       <c r="X19" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="Y19" s="26" t="s">
         <v>238</v>
       </c>
+      <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
+      <c r="AA19" s="16" t="s">
+        <v>197</v>
+      </c>
       <c r="AB19" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="AC19" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="AE19">
+      <c r="AD19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AB20" s="16"/>
-    </row>
-    <row r="21" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AB21" s="16"/>
-    </row>
-    <row r="22" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AB22" s="16"/>
-    </row>
-    <row r="23" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AB23" s="16"/>
-    </row>
-    <row r="24" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" ht="15.75" customHeight="1">
+      <c r="AA20" s="16"/>
+    </row>
+    <row r="21" spans="1:30" ht="15.75" customHeight="1">
+      <c r="AA21" s="16"/>
+    </row>
+    <row r="22" spans="1:30" ht="15.75" customHeight="1">
+      <c r="AA22" s="16"/>
+    </row>
+    <row r="23" spans="1:30" ht="15.75" customHeight="1">
+      <c r="AA23" s="16"/>
+    </row>
+    <row r="24" spans="1:30" ht="15.75" customHeight="1">
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -3977,7 +4060,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AC1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="1" max="7" width="10.59765625" customWidth="1"/>
     <col min="8" max="8" width="22.796875" bestFit="1" customWidth="1"/>
@@ -3996,7 +4079,7 @@
     <col min="29" max="29" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4085,7 +4168,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" ht="12.75" customHeight="1">
       <c r="B2" s="1" t="s">
         <v>28</v>
       </c>
@@ -4129,7 +4212,7 @@
       <c r="AA2" s="20"/>
       <c r="AB2" s="20"/>
     </row>
-    <row r="3" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="12.75" customHeight="1">
       <c r="B3" s="1" t="s">
         <v>208</v>
       </c>
@@ -4151,7 +4234,7 @@
       <c r="AA3" s="20"/>
       <c r="AB3" s="20"/>
     </row>
-    <row r="4" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="12.75" customHeight="1">
       <c r="G4" s="1" t="s">
         <v>129</v>
       </c>
@@ -4170,7 +4253,7 @@
       <c r="AA4" s="20"/>
       <c r="AB4" s="20"/>
     </row>
-    <row r="5" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="12.75" customHeight="1">
       <c r="G5" s="1" t="s">
         <v>216</v>
       </c>
@@ -4189,7 +4272,7 @@
       <c r="AA5" s="20"/>
       <c r="AB5" s="20"/>
     </row>
-    <row r="6" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="12.75" customHeight="1">
       <c r="T6" s="1" t="s">
         <v>220</v>
       </c>
@@ -4198,3979 +4281,3979 @@
       <c r="AA6" s="20"/>
       <c r="AB6" s="20"/>
     </row>
-    <row r="7" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="12.75" customHeight="1">
       <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
     </row>
-    <row r="8" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="12.75" customHeight="1">
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
     </row>
-    <row r="9" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="12.75" customHeight="1">
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
     </row>
-    <row r="10" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="12.75" customHeight="1">
       <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
     </row>
-    <row r="11" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="12.75" customHeight="1">
       <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
     </row>
-    <row r="12" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="12.75" customHeight="1">
       <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
     </row>
-    <row r="13" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" ht="12.75" customHeight="1">
       <c r="AA13" s="20"/>
       <c r="AB13" s="20"/>
     </row>
-    <row r="14" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="12.75" customHeight="1">
       <c r="AA14" s="20"/>
       <c r="AB14" s="20"/>
     </row>
-    <row r="15" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="12.75" customHeight="1">
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
     </row>
-    <row r="16" spans="1:29" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="12.75" customHeight="1">
       <c r="AA16" s="20"/>
       <c r="AB16" s="20"/>
     </row>
-    <row r="17" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA17" s="20"/>
       <c r="AB17" s="20"/>
     </row>
-    <row r="18" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
     </row>
-    <row r="19" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA19" s="20"/>
       <c r="AB19" s="20"/>
     </row>
-    <row r="20" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA20" s="20"/>
       <c r="AB20" s="20"/>
     </row>
-    <row r="21" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA21" s="20"/>
       <c r="AB21" s="20"/>
     </row>
-    <row r="22" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA22" s="20"/>
       <c r="AB22" s="20"/>
     </row>
-    <row r="23" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA23" s="20"/>
       <c r="AB23" s="20"/>
     </row>
-    <row r="24" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA24" s="20"/>
       <c r="AB24" s="20"/>
     </row>
-    <row r="25" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA25" s="20"/>
       <c r="AB25" s="20"/>
     </row>
-    <row r="26" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA26" s="20"/>
       <c r="AB26" s="20"/>
     </row>
-    <row r="27" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA27" s="20"/>
       <c r="AB27" s="20"/>
     </row>
-    <row r="28" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA28" s="20"/>
       <c r="AB28" s="20"/>
     </row>
-    <row r="29" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA29" s="20"/>
       <c r="AB29" s="20"/>
     </row>
-    <row r="30" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA30" s="20"/>
       <c r="AB30" s="20"/>
     </row>
-    <row r="31" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA31" s="20"/>
       <c r="AB31" s="20"/>
     </row>
-    <row r="32" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA32" s="20"/>
       <c r="AB32" s="20"/>
     </row>
-    <row r="33" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA33" s="20"/>
       <c r="AB33" s="20"/>
     </row>
-    <row r="34" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA34" s="20"/>
       <c r="AB34" s="20"/>
     </row>
-    <row r="35" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA35" s="20"/>
       <c r="AB35" s="20"/>
     </row>
-    <row r="36" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA36" s="20"/>
       <c r="AB36" s="20"/>
     </row>
-    <row r="37" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA37" s="20"/>
       <c r="AB37" s="20"/>
     </row>
-    <row r="38" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA38" s="20"/>
       <c r="AB38" s="20"/>
     </row>
-    <row r="39" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA39" s="20"/>
       <c r="AB39" s="20"/>
     </row>
-    <row r="40" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA40" s="20"/>
       <c r="AB40" s="20"/>
     </row>
-    <row r="41" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA41" s="20"/>
       <c r="AB41" s="20"/>
     </row>
-    <row r="42" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA42" s="20"/>
       <c r="AB42" s="20"/>
     </row>
-    <row r="43" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA43" s="20"/>
       <c r="AB43" s="20"/>
     </row>
-    <row r="44" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA44" s="20"/>
       <c r="AB44" s="20"/>
     </row>
-    <row r="45" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA45" s="20"/>
       <c r="AB45" s="20"/>
     </row>
-    <row r="46" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA46" s="20"/>
       <c r="AB46" s="20"/>
     </row>
-    <row r="47" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA47" s="20"/>
       <c r="AB47" s="20"/>
     </row>
-    <row r="48" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA48" s="20"/>
       <c r="AB48" s="20"/>
     </row>
-    <row r="49" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA49" s="20"/>
       <c r="AB49" s="20"/>
     </row>
-    <row r="50" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA50" s="20"/>
       <c r="AB50" s="20"/>
     </row>
-    <row r="51" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA51" s="20"/>
       <c r="AB51" s="20"/>
     </row>
-    <row r="52" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA52" s="20"/>
       <c r="AB52" s="20"/>
     </row>
-    <row r="53" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA53" s="20"/>
       <c r="AB53" s="20"/>
     </row>
-    <row r="54" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA54" s="20"/>
       <c r="AB54" s="20"/>
     </row>
-    <row r="55" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA55" s="20"/>
       <c r="AB55" s="20"/>
     </row>
-    <row r="56" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA56" s="20"/>
       <c r="AB56" s="20"/>
     </row>
-    <row r="57" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA57" s="20"/>
       <c r="AB57" s="20"/>
     </row>
-    <row r="58" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA58" s="20"/>
       <c r="AB58" s="20"/>
     </row>
-    <row r="59" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA59" s="20"/>
       <c r="AB59" s="20"/>
     </row>
-    <row r="60" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA60" s="20"/>
       <c r="AB60" s="20"/>
     </row>
-    <row r="61" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA61" s="20"/>
       <c r="AB61" s="20"/>
     </row>
-    <row r="62" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA62" s="20"/>
       <c r="AB62" s="20"/>
     </row>
-    <row r="63" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA63" s="20"/>
       <c r="AB63" s="20"/>
     </row>
-    <row r="64" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA64" s="20"/>
       <c r="AB64" s="20"/>
     </row>
-    <row r="65" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA65" s="20"/>
       <c r="AB65" s="20"/>
     </row>
-    <row r="66" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA66" s="20"/>
       <c r="AB66" s="20"/>
     </row>
-    <row r="67" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA67" s="20"/>
       <c r="AB67" s="20"/>
     </row>
-    <row r="68" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA68" s="20"/>
       <c r="AB68" s="20"/>
     </row>
-    <row r="69" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA69" s="20"/>
       <c r="AB69" s="20"/>
     </row>
-    <row r="70" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA70" s="20"/>
       <c r="AB70" s="20"/>
     </row>
-    <row r="71" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA71" s="20"/>
       <c r="AB71" s="20"/>
     </row>
-    <row r="72" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA72" s="20"/>
       <c r="AB72" s="20"/>
     </row>
-    <row r="73" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA73" s="20"/>
       <c r="AB73" s="20"/>
     </row>
-    <row r="74" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA74" s="20"/>
       <c r="AB74" s="20"/>
     </row>
-    <row r="75" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA75" s="20"/>
       <c r="AB75" s="20"/>
     </row>
-    <row r="76" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA76" s="20"/>
       <c r="AB76" s="20"/>
     </row>
-    <row r="77" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA77" s="20"/>
       <c r="AB77" s="20"/>
     </row>
-    <row r="78" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA78" s="20"/>
       <c r="AB78" s="20"/>
     </row>
-    <row r="79" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA79" s="20"/>
       <c r="AB79" s="20"/>
     </row>
-    <row r="80" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA80" s="20"/>
       <c r="AB80" s="20"/>
     </row>
-    <row r="81" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA81" s="20"/>
       <c r="AB81" s="20"/>
     </row>
-    <row r="82" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA82" s="20"/>
       <c r="AB82" s="20"/>
     </row>
-    <row r="83" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA83" s="20"/>
       <c r="AB83" s="20"/>
     </row>
-    <row r="84" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA84" s="20"/>
       <c r="AB84" s="20"/>
     </row>
-    <row r="85" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA85" s="20"/>
       <c r="AB85" s="20"/>
     </row>
-    <row r="86" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA86" s="20"/>
       <c r="AB86" s="20"/>
     </row>
-    <row r="87" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA87" s="20"/>
       <c r="AB87" s="20"/>
     </row>
-    <row r="88" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA88" s="20"/>
       <c r="AB88" s="20"/>
     </row>
-    <row r="89" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA89" s="20"/>
       <c r="AB89" s="20"/>
     </row>
-    <row r="90" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA90" s="20"/>
       <c r="AB90" s="20"/>
     </row>
-    <row r="91" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA91" s="20"/>
       <c r="AB91" s="20"/>
     </row>
-    <row r="92" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA92" s="20"/>
       <c r="AB92" s="20"/>
     </row>
-    <row r="93" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA93" s="20"/>
       <c r="AB93" s="20"/>
     </row>
-    <row r="94" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA94" s="20"/>
       <c r="AB94" s="20"/>
     </row>
-    <row r="95" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA95" s="20"/>
       <c r="AB95" s="20"/>
     </row>
-    <row r="96" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA96" s="20"/>
       <c r="AB96" s="20"/>
     </row>
-    <row r="97" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA97" s="20"/>
       <c r="AB97" s="20"/>
     </row>
-    <row r="98" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA98" s="20"/>
       <c r="AB98" s="20"/>
     </row>
-    <row r="99" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA99" s="20"/>
       <c r="AB99" s="20"/>
     </row>
-    <row r="100" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA100" s="20"/>
       <c r="AB100" s="20"/>
     </row>
-    <row r="101" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA101" s="20"/>
       <c r="AB101" s="20"/>
     </row>
-    <row r="102" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA102" s="20"/>
       <c r="AB102" s="20"/>
     </row>
-    <row r="103" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA103" s="20"/>
       <c r="AB103" s="20"/>
     </row>
-    <row r="104" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA104" s="20"/>
       <c r="AB104" s="20"/>
     </row>
-    <row r="105" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA105" s="20"/>
       <c r="AB105" s="20"/>
     </row>
-    <row r="106" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA106" s="20"/>
       <c r="AB106" s="20"/>
     </row>
-    <row r="107" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA107" s="20"/>
       <c r="AB107" s="20"/>
     </row>
-    <row r="108" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA108" s="20"/>
       <c r="AB108" s="20"/>
     </row>
-    <row r="109" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA109" s="20"/>
       <c r="AB109" s="20"/>
     </row>
-    <row r="110" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA110" s="20"/>
       <c r="AB110" s="20"/>
     </row>
-    <row r="111" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA111" s="20"/>
       <c r="AB111" s="20"/>
     </row>
-    <row r="112" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA112" s="20"/>
       <c r="AB112" s="20"/>
     </row>
-    <row r="113" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA113" s="20"/>
       <c r="AB113" s="20"/>
     </row>
-    <row r="114" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA114" s="20"/>
       <c r="AB114" s="20"/>
     </row>
-    <row r="115" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA115" s="20"/>
       <c r="AB115" s="20"/>
     </row>
-    <row r="116" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA116" s="20"/>
       <c r="AB116" s="20"/>
     </row>
-    <row r="117" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA117" s="20"/>
       <c r="AB117" s="20"/>
     </row>
-    <row r="118" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA118" s="20"/>
       <c r="AB118" s="20"/>
     </row>
-    <row r="119" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA119" s="20"/>
       <c r="AB119" s="20"/>
     </row>
-    <row r="120" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA120" s="20"/>
       <c r="AB120" s="20"/>
     </row>
-    <row r="121" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA121" s="20"/>
       <c r="AB121" s="20"/>
     </row>
-    <row r="122" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA122" s="20"/>
       <c r="AB122" s="20"/>
     </row>
-    <row r="123" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA123" s="20"/>
       <c r="AB123" s="20"/>
     </row>
-    <row r="124" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA124" s="20"/>
       <c r="AB124" s="20"/>
     </row>
-    <row r="125" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA125" s="20"/>
       <c r="AB125" s="20"/>
     </row>
-    <row r="126" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA126" s="20"/>
       <c r="AB126" s="20"/>
     </row>
-    <row r="127" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA127" s="20"/>
       <c r="AB127" s="20"/>
     </row>
-    <row r="128" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA128" s="20"/>
       <c r="AB128" s="20"/>
     </row>
-    <row r="129" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA129" s="20"/>
       <c r="AB129" s="20"/>
     </row>
-    <row r="130" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA130" s="20"/>
       <c r="AB130" s="20"/>
     </row>
-    <row r="131" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA131" s="20"/>
       <c r="AB131" s="20"/>
     </row>
-    <row r="132" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA132" s="20"/>
       <c r="AB132" s="20"/>
     </row>
-    <row r="133" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA133" s="20"/>
       <c r="AB133" s="20"/>
     </row>
-    <row r="134" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA134" s="20"/>
       <c r="AB134" s="20"/>
     </row>
-    <row r="135" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA135" s="20"/>
       <c r="AB135" s="20"/>
     </row>
-    <row r="136" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA136" s="20"/>
       <c r="AB136" s="20"/>
     </row>
-    <row r="137" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA137" s="20"/>
       <c r="AB137" s="20"/>
     </row>
-    <row r="138" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA138" s="20"/>
       <c r="AB138" s="20"/>
     </row>
-    <row r="139" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA139" s="20"/>
       <c r="AB139" s="20"/>
     </row>
-    <row r="140" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA140" s="20"/>
       <c r="AB140" s="20"/>
     </row>
-    <row r="141" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA141" s="20"/>
       <c r="AB141" s="20"/>
     </row>
-    <row r="142" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA142" s="20"/>
       <c r="AB142" s="20"/>
     </row>
-    <row r="143" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA143" s="20"/>
       <c r="AB143" s="20"/>
     </row>
-    <row r="144" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA144" s="20"/>
       <c r="AB144" s="20"/>
     </row>
-    <row r="145" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA145" s="20"/>
       <c r="AB145" s="20"/>
     </row>
-    <row r="146" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA146" s="20"/>
       <c r="AB146" s="20"/>
     </row>
-    <row r="147" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA147" s="20"/>
       <c r="AB147" s="20"/>
     </row>
-    <row r="148" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA148" s="20"/>
       <c r="AB148" s="20"/>
     </row>
-    <row r="149" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA149" s="20"/>
       <c r="AB149" s="20"/>
     </row>
-    <row r="150" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA150" s="20"/>
       <c r="AB150" s="20"/>
     </row>
-    <row r="151" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA151" s="20"/>
       <c r="AB151" s="20"/>
     </row>
-    <row r="152" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA152" s="20"/>
       <c r="AB152" s="20"/>
     </row>
-    <row r="153" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA153" s="20"/>
       <c r="AB153" s="20"/>
     </row>
-    <row r="154" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA154" s="20"/>
       <c r="AB154" s="20"/>
     </row>
-    <row r="155" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA155" s="20"/>
       <c r="AB155" s="20"/>
     </row>
-    <row r="156" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA156" s="20"/>
       <c r="AB156" s="20"/>
     </row>
-    <row r="157" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA157" s="20"/>
       <c r="AB157" s="20"/>
     </row>
-    <row r="158" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA158" s="20"/>
       <c r="AB158" s="20"/>
     </row>
-    <row r="159" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA159" s="20"/>
       <c r="AB159" s="20"/>
     </row>
-    <row r="160" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA160" s="20"/>
       <c r="AB160" s="20"/>
     </row>
-    <row r="161" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA161" s="20"/>
       <c r="AB161" s="20"/>
     </row>
-    <row r="162" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA162" s="20"/>
       <c r="AB162" s="20"/>
     </row>
-    <row r="163" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA163" s="20"/>
       <c r="AB163" s="20"/>
     </row>
-    <row r="164" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA164" s="20"/>
       <c r="AB164" s="20"/>
     </row>
-    <row r="165" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA165" s="20"/>
       <c r="AB165" s="20"/>
     </row>
-    <row r="166" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA166" s="20"/>
       <c r="AB166" s="20"/>
     </row>
-    <row r="167" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA167" s="20"/>
       <c r="AB167" s="20"/>
     </row>
-    <row r="168" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA168" s="20"/>
       <c r="AB168" s="20"/>
     </row>
-    <row r="169" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA169" s="20"/>
       <c r="AB169" s="20"/>
     </row>
-    <row r="170" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA170" s="20"/>
       <c r="AB170" s="20"/>
     </row>
-    <row r="171" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA171" s="20"/>
       <c r="AB171" s="20"/>
     </row>
-    <row r="172" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA172" s="20"/>
       <c r="AB172" s="20"/>
     </row>
-    <row r="173" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA173" s="20"/>
       <c r="AB173" s="20"/>
     </row>
-    <row r="174" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA174" s="20"/>
       <c r="AB174" s="20"/>
     </row>
-    <row r="175" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA175" s="20"/>
       <c r="AB175" s="20"/>
     </row>
-    <row r="176" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA176" s="20"/>
       <c r="AB176" s="20"/>
     </row>
-    <row r="177" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA177" s="20"/>
       <c r="AB177" s="20"/>
     </row>
-    <row r="178" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA178" s="20"/>
       <c r="AB178" s="20"/>
     </row>
-    <row r="179" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA179" s="20"/>
       <c r="AB179" s="20"/>
     </row>
-    <row r="180" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA180" s="20"/>
       <c r="AB180" s="20"/>
     </row>
-    <row r="181" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA181" s="20"/>
       <c r="AB181" s="20"/>
     </row>
-    <row r="182" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA182" s="20"/>
       <c r="AB182" s="20"/>
     </row>
-    <row r="183" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA183" s="20"/>
       <c r="AB183" s="20"/>
     </row>
-    <row r="184" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA184" s="20"/>
       <c r="AB184" s="20"/>
     </row>
-    <row r="185" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA185" s="20"/>
       <c r="AB185" s="20"/>
     </row>
-    <row r="186" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA186" s="20"/>
       <c r="AB186" s="20"/>
     </row>
-    <row r="187" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA187" s="20"/>
       <c r="AB187" s="20"/>
     </row>
-    <row r="188" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA188" s="20"/>
       <c r="AB188" s="20"/>
     </row>
-    <row r="189" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA189" s="20"/>
       <c r="AB189" s="20"/>
     </row>
-    <row r="190" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA190" s="20"/>
       <c r="AB190" s="20"/>
     </row>
-    <row r="191" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA191" s="20"/>
       <c r="AB191" s="20"/>
     </row>
-    <row r="192" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA192" s="20"/>
       <c r="AB192" s="20"/>
     </row>
-    <row r="193" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA193" s="20"/>
       <c r="AB193" s="20"/>
     </row>
-    <row r="194" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA194" s="20"/>
       <c r="AB194" s="20"/>
     </row>
-    <row r="195" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA195" s="20"/>
       <c r="AB195" s="20"/>
     </row>
-    <row r="196" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA196" s="20"/>
       <c r="AB196" s="20"/>
     </row>
-    <row r="197" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA197" s="20"/>
       <c r="AB197" s="20"/>
     </row>
-    <row r="198" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA198" s="20"/>
       <c r="AB198" s="20"/>
     </row>
-    <row r="199" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA199" s="20"/>
       <c r="AB199" s="20"/>
     </row>
-    <row r="200" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA200" s="20"/>
       <c r="AB200" s="20"/>
     </row>
-    <row r="201" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA201" s="20"/>
       <c r="AB201" s="20"/>
     </row>
-    <row r="202" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA202" s="20"/>
       <c r="AB202" s="20"/>
     </row>
-    <row r="203" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA203" s="20"/>
       <c r="AB203" s="20"/>
     </row>
-    <row r="204" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA204" s="20"/>
       <c r="AB204" s="20"/>
     </row>
-    <row r="205" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA205" s="20"/>
       <c r="AB205" s="20"/>
     </row>
-    <row r="206" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA206" s="20"/>
       <c r="AB206" s="20"/>
     </row>
-    <row r="207" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA207" s="20"/>
       <c r="AB207" s="20"/>
     </row>
-    <row r="208" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA208" s="20"/>
       <c r="AB208" s="20"/>
     </row>
-    <row r="209" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA209" s="20"/>
       <c r="AB209" s="20"/>
     </row>
-    <row r="210" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA210" s="20"/>
       <c r="AB210" s="20"/>
     </row>
-    <row r="211" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA211" s="20"/>
       <c r="AB211" s="20"/>
     </row>
-    <row r="212" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA212" s="20"/>
       <c r="AB212" s="20"/>
     </row>
-    <row r="213" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA213" s="20"/>
       <c r="AB213" s="20"/>
     </row>
-    <row r="214" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA214" s="20"/>
       <c r="AB214" s="20"/>
     </row>
-    <row r="215" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA215" s="20"/>
       <c r="AB215" s="20"/>
     </row>
-    <row r="216" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA216" s="20"/>
       <c r="AB216" s="20"/>
     </row>
-    <row r="217" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA217" s="20"/>
       <c r="AB217" s="20"/>
     </row>
-    <row r="218" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA218" s="20"/>
       <c r="AB218" s="20"/>
     </row>
-    <row r="219" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA219" s="20"/>
       <c r="AB219" s="20"/>
     </row>
-    <row r="220" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA220" s="20"/>
       <c r="AB220" s="20"/>
     </row>
-    <row r="221" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA221" s="20"/>
       <c r="AB221" s="20"/>
     </row>
-    <row r="222" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA222" s="20"/>
       <c r="AB222" s="20"/>
     </row>
-    <row r="223" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA223" s="20"/>
       <c r="AB223" s="20"/>
     </row>
-    <row r="224" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA224" s="20"/>
       <c r="AB224" s="20"/>
     </row>
-    <row r="225" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA225" s="20"/>
       <c r="AB225" s="20"/>
     </row>
-    <row r="226" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA226" s="20"/>
       <c r="AB226" s="20"/>
     </row>
-    <row r="227" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA227" s="20"/>
       <c r="AB227" s="20"/>
     </row>
-    <row r="228" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA228" s="20"/>
       <c r="AB228" s="20"/>
     </row>
-    <row r="229" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA229" s="20"/>
       <c r="AB229" s="20"/>
     </row>
-    <row r="230" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA230" s="20"/>
       <c r="AB230" s="20"/>
     </row>
-    <row r="231" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA231" s="20"/>
       <c r="AB231" s="20"/>
     </row>
-    <row r="232" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA232" s="20"/>
       <c r="AB232" s="20"/>
     </row>
-    <row r="233" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA233" s="20"/>
       <c r="AB233" s="20"/>
     </row>
-    <row r="234" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA234" s="20"/>
       <c r="AB234" s="20"/>
     </row>
-    <row r="235" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA235" s="20"/>
       <c r="AB235" s="20"/>
     </row>
-    <row r="236" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA236" s="20"/>
       <c r="AB236" s="20"/>
     </row>
-    <row r="237" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA237" s="20"/>
       <c r="AB237" s="20"/>
     </row>
-    <row r="238" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA238" s="20"/>
       <c r="AB238" s="20"/>
     </row>
-    <row r="239" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA239" s="20"/>
       <c r="AB239" s="20"/>
     </row>
-    <row r="240" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA240" s="20"/>
       <c r="AB240" s="20"/>
     </row>
-    <row r="241" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA241" s="20"/>
       <c r="AB241" s="20"/>
     </row>
-    <row r="242" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA242" s="20"/>
       <c r="AB242" s="20"/>
     </row>
-    <row r="243" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA243" s="20"/>
       <c r="AB243" s="20"/>
     </row>
-    <row r="244" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA244" s="20"/>
       <c r="AB244" s="20"/>
     </row>
-    <row r="245" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA245" s="20"/>
       <c r="AB245" s="20"/>
     </row>
-    <row r="246" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA246" s="20"/>
       <c r="AB246" s="20"/>
     </row>
-    <row r="247" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA247" s="20"/>
       <c r="AB247" s="20"/>
     </row>
-    <row r="248" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA248" s="20"/>
       <c r="AB248" s="20"/>
     </row>
-    <row r="249" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA249" s="20"/>
       <c r="AB249" s="20"/>
     </row>
-    <row r="250" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA250" s="20"/>
       <c r="AB250" s="20"/>
     </row>
-    <row r="251" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA251" s="20"/>
       <c r="AB251" s="20"/>
     </row>
-    <row r="252" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA252" s="20"/>
       <c r="AB252" s="20"/>
     </row>
-    <row r="253" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA253" s="20"/>
       <c r="AB253" s="20"/>
     </row>
-    <row r="254" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA254" s="20"/>
       <c r="AB254" s="20"/>
     </row>
-    <row r="255" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA255" s="20"/>
       <c r="AB255" s="20"/>
     </row>
-    <row r="256" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA256" s="20"/>
       <c r="AB256" s="20"/>
     </row>
-    <row r="257" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA257" s="20"/>
       <c r="AB257" s="20"/>
     </row>
-    <row r="258" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA258" s="20"/>
       <c r="AB258" s="20"/>
     </row>
-    <row r="259" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA259" s="20"/>
       <c r="AB259" s="20"/>
     </row>
-    <row r="260" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA260" s="20"/>
       <c r="AB260" s="20"/>
     </row>
-    <row r="261" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA261" s="20"/>
       <c r="AB261" s="20"/>
     </row>
-    <row r="262" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA262" s="20"/>
       <c r="AB262" s="20"/>
     </row>
-    <row r="263" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA263" s="20"/>
       <c r="AB263" s="20"/>
     </row>
-    <row r="264" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA264" s="20"/>
       <c r="AB264" s="20"/>
     </row>
-    <row r="265" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA265" s="20"/>
       <c r="AB265" s="20"/>
     </row>
-    <row r="266" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA266" s="20"/>
       <c r="AB266" s="20"/>
     </row>
-    <row r="267" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA267" s="20"/>
       <c r="AB267" s="20"/>
     </row>
-    <row r="268" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA268" s="20"/>
       <c r="AB268" s="20"/>
     </row>
-    <row r="269" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA269" s="20"/>
       <c r="AB269" s="20"/>
     </row>
-    <row r="270" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA270" s="20"/>
       <c r="AB270" s="20"/>
     </row>
-    <row r="271" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA271" s="20"/>
       <c r="AB271" s="20"/>
     </row>
-    <row r="272" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA272" s="20"/>
       <c r="AB272" s="20"/>
     </row>
-    <row r="273" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA273" s="20"/>
       <c r="AB273" s="20"/>
     </row>
-    <row r="274" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA274" s="20"/>
       <c r="AB274" s="20"/>
     </row>
-    <row r="275" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA275" s="20"/>
       <c r="AB275" s="20"/>
     </row>
-    <row r="276" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA276" s="20"/>
       <c r="AB276" s="20"/>
     </row>
-    <row r="277" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA277" s="20"/>
       <c r="AB277" s="20"/>
     </row>
-    <row r="278" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA278" s="20"/>
       <c r="AB278" s="20"/>
     </row>
-    <row r="279" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA279" s="20"/>
       <c r="AB279" s="20"/>
     </row>
-    <row r="280" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA280" s="20"/>
       <c r="AB280" s="20"/>
     </row>
-    <row r="281" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA281" s="20"/>
       <c r="AB281" s="20"/>
     </row>
-    <row r="282" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA282" s="20"/>
       <c r="AB282" s="20"/>
     </row>
-    <row r="283" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA283" s="20"/>
       <c r="AB283" s="20"/>
     </row>
-    <row r="284" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA284" s="20"/>
       <c r="AB284" s="20"/>
     </row>
-    <row r="285" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA285" s="20"/>
       <c r="AB285" s="20"/>
     </row>
-    <row r="286" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA286" s="20"/>
       <c r="AB286" s="20"/>
     </row>
-    <row r="287" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA287" s="20"/>
       <c r="AB287" s="20"/>
     </row>
-    <row r="288" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA288" s="20"/>
       <c r="AB288" s="20"/>
     </row>
-    <row r="289" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA289" s="20"/>
       <c r="AB289" s="20"/>
     </row>
-    <row r="290" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA290" s="20"/>
       <c r="AB290" s="20"/>
     </row>
-    <row r="291" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA291" s="20"/>
       <c r="AB291" s="20"/>
     </row>
-    <row r="292" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA292" s="20"/>
       <c r="AB292" s="20"/>
     </row>
-    <row r="293" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA293" s="20"/>
       <c r="AB293" s="20"/>
     </row>
-    <row r="294" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA294" s="20"/>
       <c r="AB294" s="20"/>
     </row>
-    <row r="295" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA295" s="20"/>
       <c r="AB295" s="20"/>
     </row>
-    <row r="296" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA296" s="20"/>
       <c r="AB296" s="20"/>
     </row>
-    <row r="297" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA297" s="20"/>
       <c r="AB297" s="20"/>
     </row>
-    <row r="298" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA298" s="20"/>
       <c r="AB298" s="20"/>
     </row>
-    <row r="299" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA299" s="20"/>
       <c r="AB299" s="20"/>
     </row>
-    <row r="300" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA300" s="20"/>
       <c r="AB300" s="20"/>
     </row>
-    <row r="301" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA301" s="20"/>
       <c r="AB301" s="20"/>
     </row>
-    <row r="302" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA302" s="20"/>
       <c r="AB302" s="20"/>
     </row>
-    <row r="303" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA303" s="20"/>
       <c r="AB303" s="20"/>
     </row>
-    <row r="304" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA304" s="20"/>
       <c r="AB304" s="20"/>
     </row>
-    <row r="305" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA305" s="20"/>
       <c r="AB305" s="20"/>
     </row>
-    <row r="306" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA306" s="20"/>
       <c r="AB306" s="20"/>
     </row>
-    <row r="307" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA307" s="20"/>
       <c r="AB307" s="20"/>
     </row>
-    <row r="308" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA308" s="20"/>
       <c r="AB308" s="20"/>
     </row>
-    <row r="309" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA309" s="20"/>
       <c r="AB309" s="20"/>
     </row>
-    <row r="310" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA310" s="20"/>
       <c r="AB310" s="20"/>
     </row>
-    <row r="311" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA311" s="20"/>
       <c r="AB311" s="20"/>
     </row>
-    <row r="312" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA312" s="20"/>
       <c r="AB312" s="20"/>
     </row>
-    <row r="313" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA313" s="20"/>
       <c r="AB313" s="20"/>
     </row>
-    <row r="314" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA314" s="20"/>
       <c r="AB314" s="20"/>
     </row>
-    <row r="315" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA315" s="20"/>
       <c r="AB315" s="20"/>
     </row>
-    <row r="316" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA316" s="20"/>
       <c r="AB316" s="20"/>
     </row>
-    <row r="317" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA317" s="20"/>
       <c r="AB317" s="20"/>
     </row>
-    <row r="318" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA318" s="20"/>
       <c r="AB318" s="20"/>
     </row>
-    <row r="319" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA319" s="20"/>
       <c r="AB319" s="20"/>
     </row>
-    <row r="320" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA320" s="20"/>
       <c r="AB320" s="20"/>
     </row>
-    <row r="321" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA321" s="20"/>
       <c r="AB321" s="20"/>
     </row>
-    <row r="322" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA322" s="20"/>
       <c r="AB322" s="20"/>
     </row>
-    <row r="323" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA323" s="20"/>
       <c r="AB323" s="20"/>
     </row>
-    <row r="324" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA324" s="20"/>
       <c r="AB324" s="20"/>
     </row>
-    <row r="325" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA325" s="20"/>
       <c r="AB325" s="20"/>
     </row>
-    <row r="326" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA326" s="20"/>
       <c r="AB326" s="20"/>
     </row>
-    <row r="327" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA327" s="20"/>
       <c r="AB327" s="20"/>
     </row>
-    <row r="328" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA328" s="20"/>
       <c r="AB328" s="20"/>
     </row>
-    <row r="329" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA329" s="20"/>
       <c r="AB329" s="20"/>
     </row>
-    <row r="330" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA330" s="20"/>
       <c r="AB330" s="20"/>
     </row>
-    <row r="331" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA331" s="20"/>
       <c r="AB331" s="20"/>
     </row>
-    <row r="332" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA332" s="20"/>
       <c r="AB332" s="20"/>
     </row>
-    <row r="333" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA333" s="20"/>
       <c r="AB333" s="20"/>
     </row>
-    <row r="334" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA334" s="20"/>
       <c r="AB334" s="20"/>
     </row>
-    <row r="335" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA335" s="20"/>
       <c r="AB335" s="20"/>
     </row>
-    <row r="336" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA336" s="20"/>
       <c r="AB336" s="20"/>
     </row>
-    <row r="337" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA337" s="20"/>
       <c r="AB337" s="20"/>
     </row>
-    <row r="338" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA338" s="20"/>
       <c r="AB338" s="20"/>
     </row>
-    <row r="339" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA339" s="20"/>
       <c r="AB339" s="20"/>
     </row>
-    <row r="340" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA340" s="20"/>
       <c r="AB340" s="20"/>
     </row>
-    <row r="341" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA341" s="20"/>
       <c r="AB341" s="20"/>
     </row>
-    <row r="342" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA342" s="20"/>
       <c r="AB342" s="20"/>
     </row>
-    <row r="343" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA343" s="20"/>
       <c r="AB343" s="20"/>
     </row>
-    <row r="344" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA344" s="20"/>
       <c r="AB344" s="20"/>
     </row>
-    <row r="345" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA345" s="20"/>
       <c r="AB345" s="20"/>
     </row>
-    <row r="346" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA346" s="20"/>
       <c r="AB346" s="20"/>
     </row>
-    <row r="347" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA347" s="20"/>
       <c r="AB347" s="20"/>
     </row>
-    <row r="348" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA348" s="20"/>
       <c r="AB348" s="20"/>
     </row>
-    <row r="349" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA349" s="20"/>
       <c r="AB349" s="20"/>
     </row>
-    <row r="350" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA350" s="20"/>
       <c r="AB350" s="20"/>
     </row>
-    <row r="351" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA351" s="20"/>
       <c r="AB351" s="20"/>
     </row>
-    <row r="352" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA352" s="20"/>
       <c r="AB352" s="20"/>
     </row>
-    <row r="353" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA353" s="20"/>
       <c r="AB353" s="20"/>
     </row>
-    <row r="354" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA354" s="20"/>
       <c r="AB354" s="20"/>
     </row>
-    <row r="355" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA355" s="20"/>
       <c r="AB355" s="20"/>
     </row>
-    <row r="356" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA356" s="20"/>
       <c r="AB356" s="20"/>
     </row>
-    <row r="357" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA357" s="20"/>
       <c r="AB357" s="20"/>
     </row>
-    <row r="358" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA358" s="20"/>
       <c r="AB358" s="20"/>
     </row>
-    <row r="359" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA359" s="20"/>
       <c r="AB359" s="20"/>
     </row>
-    <row r="360" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA360" s="20"/>
       <c r="AB360" s="20"/>
     </row>
-    <row r="361" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA361" s="20"/>
       <c r="AB361" s="20"/>
     </row>
-    <row r="362" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA362" s="20"/>
       <c r="AB362" s="20"/>
     </row>
-    <row r="363" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA363" s="20"/>
       <c r="AB363" s="20"/>
     </row>
-    <row r="364" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA364" s="20"/>
       <c r="AB364" s="20"/>
     </row>
-    <row r="365" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA365" s="20"/>
       <c r="AB365" s="20"/>
     </row>
-    <row r="366" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA366" s="20"/>
       <c r="AB366" s="20"/>
     </row>
-    <row r="367" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA367" s="20"/>
       <c r="AB367" s="20"/>
     </row>
-    <row r="368" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA368" s="20"/>
       <c r="AB368" s="20"/>
     </row>
-    <row r="369" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA369" s="20"/>
       <c r="AB369" s="20"/>
     </row>
-    <row r="370" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA370" s="20"/>
       <c r="AB370" s="20"/>
     </row>
-    <row r="371" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA371" s="20"/>
       <c r="AB371" s="20"/>
     </row>
-    <row r="372" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA372" s="20"/>
       <c r="AB372" s="20"/>
     </row>
-    <row r="373" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA373" s="20"/>
       <c r="AB373" s="20"/>
     </row>
-    <row r="374" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA374" s="20"/>
       <c r="AB374" s="20"/>
     </row>
-    <row r="375" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA375" s="20"/>
       <c r="AB375" s="20"/>
     </row>
-    <row r="376" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA376" s="20"/>
       <c r="AB376" s="20"/>
     </row>
-    <row r="377" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA377" s="20"/>
       <c r="AB377" s="20"/>
     </row>
-    <row r="378" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA378" s="20"/>
       <c r="AB378" s="20"/>
     </row>
-    <row r="379" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA379" s="20"/>
       <c r="AB379" s="20"/>
     </row>
-    <row r="380" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA380" s="20"/>
       <c r="AB380" s="20"/>
     </row>
-    <row r="381" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA381" s="20"/>
       <c r="AB381" s="20"/>
     </row>
-    <row r="382" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA382" s="20"/>
       <c r="AB382" s="20"/>
     </row>
-    <row r="383" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA383" s="20"/>
       <c r="AB383" s="20"/>
     </row>
-    <row r="384" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA384" s="20"/>
       <c r="AB384" s="20"/>
     </row>
-    <row r="385" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA385" s="20"/>
       <c r="AB385" s="20"/>
     </row>
-    <row r="386" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA386" s="20"/>
       <c r="AB386" s="20"/>
     </row>
-    <row r="387" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA387" s="20"/>
       <c r="AB387" s="20"/>
     </row>
-    <row r="388" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA388" s="20"/>
       <c r="AB388" s="20"/>
     </row>
-    <row r="389" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA389" s="20"/>
       <c r="AB389" s="20"/>
     </row>
-    <row r="390" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA390" s="20"/>
       <c r="AB390" s="20"/>
     </row>
-    <row r="391" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA391" s="20"/>
       <c r="AB391" s="20"/>
     </row>
-    <row r="392" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA392" s="20"/>
       <c r="AB392" s="20"/>
     </row>
-    <row r="393" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA393" s="20"/>
       <c r="AB393" s="20"/>
     </row>
-    <row r="394" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA394" s="20"/>
       <c r="AB394" s="20"/>
     </row>
-    <row r="395" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA395" s="20"/>
       <c r="AB395" s="20"/>
     </row>
-    <row r="396" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA396" s="20"/>
       <c r="AB396" s="20"/>
     </row>
-    <row r="397" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA397" s="20"/>
       <c r="AB397" s="20"/>
     </row>
-    <row r="398" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA398" s="20"/>
       <c r="AB398" s="20"/>
     </row>
-    <row r="399" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA399" s="20"/>
       <c r="AB399" s="20"/>
     </row>
-    <row r="400" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA400" s="20"/>
       <c r="AB400" s="20"/>
     </row>
-    <row r="401" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA401" s="20"/>
       <c r="AB401" s="20"/>
     </row>
-    <row r="402" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA402" s="20"/>
       <c r="AB402" s="20"/>
     </row>
-    <row r="403" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA403" s="20"/>
       <c r="AB403" s="20"/>
     </row>
-    <row r="404" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA404" s="20"/>
       <c r="AB404" s="20"/>
     </row>
-    <row r="405" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA405" s="20"/>
       <c r="AB405" s="20"/>
     </row>
-    <row r="406" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA406" s="20"/>
       <c r="AB406" s="20"/>
     </row>
-    <row r="407" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA407" s="20"/>
       <c r="AB407" s="20"/>
     </row>
-    <row r="408" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA408" s="20"/>
       <c r="AB408" s="20"/>
     </row>
-    <row r="409" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA409" s="20"/>
       <c r="AB409" s="20"/>
     </row>
-    <row r="410" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA410" s="20"/>
       <c r="AB410" s="20"/>
     </row>
-    <row r="411" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA411" s="20"/>
       <c r="AB411" s="20"/>
     </row>
-    <row r="412" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA412" s="20"/>
       <c r="AB412" s="20"/>
     </row>
-    <row r="413" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA413" s="20"/>
       <c r="AB413" s="20"/>
     </row>
-    <row r="414" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA414" s="20"/>
       <c r="AB414" s="20"/>
     </row>
-    <row r="415" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA415" s="20"/>
       <c r="AB415" s="20"/>
     </row>
-    <row r="416" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA416" s="20"/>
       <c r="AB416" s="20"/>
     </row>
-    <row r="417" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA417" s="20"/>
       <c r="AB417" s="20"/>
     </row>
-    <row r="418" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA418" s="20"/>
       <c r="AB418" s="20"/>
     </row>
-    <row r="419" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA419" s="20"/>
       <c r="AB419" s="20"/>
     </row>
-    <row r="420" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA420" s="20"/>
       <c r="AB420" s="20"/>
     </row>
-    <row r="421" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA421" s="20"/>
       <c r="AB421" s="20"/>
     </row>
-    <row r="422" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA422" s="20"/>
       <c r="AB422" s="20"/>
     </row>
-    <row r="423" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA423" s="20"/>
       <c r="AB423" s="20"/>
     </row>
-    <row r="424" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA424" s="20"/>
       <c r="AB424" s="20"/>
     </row>
-    <row r="425" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA425" s="20"/>
       <c r="AB425" s="20"/>
     </row>
-    <row r="426" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA426" s="20"/>
       <c r="AB426" s="20"/>
     </row>
-    <row r="427" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA427" s="20"/>
       <c r="AB427" s="20"/>
     </row>
-    <row r="428" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA428" s="20"/>
       <c r="AB428" s="20"/>
     </row>
-    <row r="429" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA429" s="20"/>
       <c r="AB429" s="20"/>
     </row>
-    <row r="430" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA430" s="20"/>
       <c r="AB430" s="20"/>
     </row>
-    <row r="431" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA431" s="20"/>
       <c r="AB431" s="20"/>
     </row>
-    <row r="432" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA432" s="20"/>
       <c r="AB432" s="20"/>
     </row>
-    <row r="433" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA433" s="20"/>
       <c r="AB433" s="20"/>
     </row>
-    <row r="434" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA434" s="20"/>
       <c r="AB434" s="20"/>
     </row>
-    <row r="435" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA435" s="20"/>
       <c r="AB435" s="20"/>
     </row>
-    <row r="436" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA436" s="20"/>
       <c r="AB436" s="20"/>
     </row>
-    <row r="437" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA437" s="20"/>
       <c r="AB437" s="20"/>
     </row>
-    <row r="438" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA438" s="20"/>
       <c r="AB438" s="20"/>
     </row>
-    <row r="439" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA439" s="20"/>
       <c r="AB439" s="20"/>
     </row>
-    <row r="440" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA440" s="20"/>
       <c r="AB440" s="20"/>
     </row>
-    <row r="441" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA441" s="20"/>
       <c r="AB441" s="20"/>
     </row>
-    <row r="442" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA442" s="20"/>
       <c r="AB442" s="20"/>
     </row>
-    <row r="443" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA443" s="20"/>
       <c r="AB443" s="20"/>
     </row>
-    <row r="444" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA444" s="20"/>
       <c r="AB444" s="20"/>
     </row>
-    <row r="445" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA445" s="20"/>
       <c r="AB445" s="20"/>
     </row>
-    <row r="446" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA446" s="20"/>
       <c r="AB446" s="20"/>
     </row>
-    <row r="447" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA447" s="20"/>
       <c r="AB447" s="20"/>
     </row>
-    <row r="448" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA448" s="20"/>
       <c r="AB448" s="20"/>
     </row>
-    <row r="449" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA449" s="20"/>
       <c r="AB449" s="20"/>
     </row>
-    <row r="450" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA450" s="20"/>
       <c r="AB450" s="20"/>
     </row>
-    <row r="451" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA451" s="20"/>
       <c r="AB451" s="20"/>
     </row>
-    <row r="452" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA452" s="20"/>
       <c r="AB452" s="20"/>
     </row>
-    <row r="453" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA453" s="20"/>
       <c r="AB453" s="20"/>
     </row>
-    <row r="454" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA454" s="20"/>
       <c r="AB454" s="20"/>
     </row>
-    <row r="455" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA455" s="20"/>
       <c r="AB455" s="20"/>
     </row>
-    <row r="456" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA456" s="20"/>
       <c r="AB456" s="20"/>
     </row>
-    <row r="457" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA457" s="20"/>
       <c r="AB457" s="20"/>
     </row>
-    <row r="458" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA458" s="20"/>
       <c r="AB458" s="20"/>
     </row>
-    <row r="459" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA459" s="20"/>
       <c r="AB459" s="20"/>
     </row>
-    <row r="460" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA460" s="20"/>
       <c r="AB460" s="20"/>
     </row>
-    <row r="461" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA461" s="20"/>
       <c r="AB461" s="20"/>
     </row>
-    <row r="462" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA462" s="20"/>
       <c r="AB462" s="20"/>
     </row>
-    <row r="463" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA463" s="20"/>
       <c r="AB463" s="20"/>
     </row>
-    <row r="464" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA464" s="20"/>
       <c r="AB464" s="20"/>
     </row>
-    <row r="465" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA465" s="20"/>
       <c r="AB465" s="20"/>
     </row>
-    <row r="466" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA466" s="20"/>
       <c r="AB466" s="20"/>
     </row>
-    <row r="467" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA467" s="20"/>
       <c r="AB467" s="20"/>
     </row>
-    <row r="468" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA468" s="20"/>
       <c r="AB468" s="20"/>
     </row>
-    <row r="469" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA469" s="20"/>
       <c r="AB469" s="20"/>
     </row>
-    <row r="470" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA470" s="20"/>
       <c r="AB470" s="20"/>
     </row>
-    <row r="471" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA471" s="20"/>
       <c r="AB471" s="20"/>
     </row>
-    <row r="472" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA472" s="20"/>
       <c r="AB472" s="20"/>
     </row>
-    <row r="473" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA473" s="20"/>
       <c r="AB473" s="20"/>
     </row>
-    <row r="474" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA474" s="20"/>
       <c r="AB474" s="20"/>
     </row>
-    <row r="475" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA475" s="20"/>
       <c r="AB475" s="20"/>
     </row>
-    <row r="476" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA476" s="20"/>
       <c r="AB476" s="20"/>
     </row>
-    <row r="477" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA477" s="20"/>
       <c r="AB477" s="20"/>
     </row>
-    <row r="478" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA478" s="20"/>
       <c r="AB478" s="20"/>
     </row>
-    <row r="479" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA479" s="20"/>
       <c r="AB479" s="20"/>
     </row>
-    <row r="480" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA480" s="20"/>
       <c r="AB480" s="20"/>
     </row>
-    <row r="481" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA481" s="20"/>
       <c r="AB481" s="20"/>
     </row>
-    <row r="482" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA482" s="20"/>
       <c r="AB482" s="20"/>
     </row>
-    <row r="483" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA483" s="20"/>
       <c r="AB483" s="20"/>
     </row>
-    <row r="484" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA484" s="20"/>
       <c r="AB484" s="20"/>
     </row>
-    <row r="485" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA485" s="20"/>
       <c r="AB485" s="20"/>
     </row>
-    <row r="486" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA486" s="20"/>
       <c r="AB486" s="20"/>
     </row>
-    <row r="487" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA487" s="20"/>
       <c r="AB487" s="20"/>
     </row>
-    <row r="488" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA488" s="20"/>
       <c r="AB488" s="20"/>
     </row>
-    <row r="489" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA489" s="20"/>
       <c r="AB489" s="20"/>
     </row>
-    <row r="490" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA490" s="20"/>
       <c r="AB490" s="20"/>
     </row>
-    <row r="491" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA491" s="20"/>
       <c r="AB491" s="20"/>
     </row>
-    <row r="492" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA492" s="20"/>
       <c r="AB492" s="20"/>
     </row>
-    <row r="493" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA493" s="20"/>
       <c r="AB493" s="20"/>
     </row>
-    <row r="494" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA494" s="20"/>
       <c r="AB494" s="20"/>
     </row>
-    <row r="495" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA495" s="20"/>
       <c r="AB495" s="20"/>
     </row>
-    <row r="496" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA496" s="20"/>
       <c r="AB496" s="20"/>
     </row>
-    <row r="497" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA497" s="20"/>
       <c r="AB497" s="20"/>
     </row>
-    <row r="498" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA498" s="20"/>
       <c r="AB498" s="20"/>
     </row>
-    <row r="499" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA499" s="20"/>
       <c r="AB499" s="20"/>
     </row>
-    <row r="500" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA500" s="20"/>
       <c r="AB500" s="20"/>
     </row>
-    <row r="501" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA501" s="20"/>
       <c r="AB501" s="20"/>
     </row>
-    <row r="502" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA502" s="20"/>
       <c r="AB502" s="20"/>
     </row>
-    <row r="503" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA503" s="20"/>
       <c r="AB503" s="20"/>
     </row>
-    <row r="504" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA504" s="20"/>
       <c r="AB504" s="20"/>
     </row>
-    <row r="505" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA505" s="20"/>
       <c r="AB505" s="20"/>
     </row>
-    <row r="506" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA506" s="20"/>
       <c r="AB506" s="20"/>
     </row>
-    <row r="507" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA507" s="20"/>
       <c r="AB507" s="20"/>
     </row>
-    <row r="508" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA508" s="20"/>
       <c r="AB508" s="20"/>
     </row>
-    <row r="509" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA509" s="20"/>
       <c r="AB509" s="20"/>
     </row>
-    <row r="510" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA510" s="20"/>
       <c r="AB510" s="20"/>
     </row>
-    <row r="511" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA511" s="20"/>
       <c r="AB511" s="20"/>
     </row>
-    <row r="512" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA512" s="20"/>
       <c r="AB512" s="20"/>
     </row>
-    <row r="513" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA513" s="20"/>
       <c r="AB513" s="20"/>
     </row>
-    <row r="514" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA514" s="20"/>
       <c r="AB514" s="20"/>
     </row>
-    <row r="515" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA515" s="20"/>
       <c r="AB515" s="20"/>
     </row>
-    <row r="516" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA516" s="20"/>
       <c r="AB516" s="20"/>
     </row>
-    <row r="517" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA517" s="20"/>
       <c r="AB517" s="20"/>
     </row>
-    <row r="518" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA518" s="20"/>
       <c r="AB518" s="20"/>
     </row>
-    <row r="519" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA519" s="20"/>
       <c r="AB519" s="20"/>
     </row>
-    <row r="520" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA520" s="20"/>
       <c r="AB520" s="20"/>
     </row>
-    <row r="521" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA521" s="20"/>
       <c r="AB521" s="20"/>
     </row>
-    <row r="522" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA522" s="20"/>
       <c r="AB522" s="20"/>
     </row>
-    <row r="523" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA523" s="20"/>
       <c r="AB523" s="20"/>
     </row>
-    <row r="524" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA524" s="20"/>
       <c r="AB524" s="20"/>
     </row>
-    <row r="525" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA525" s="20"/>
       <c r="AB525" s="20"/>
     </row>
-    <row r="526" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA526" s="20"/>
       <c r="AB526" s="20"/>
     </row>
-    <row r="527" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA527" s="20"/>
       <c r="AB527" s="20"/>
     </row>
-    <row r="528" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA528" s="20"/>
       <c r="AB528" s="20"/>
     </row>
-    <row r="529" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA529" s="20"/>
       <c r="AB529" s="20"/>
     </row>
-    <row r="530" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA530" s="20"/>
       <c r="AB530" s="20"/>
     </row>
-    <row r="531" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA531" s="20"/>
       <c r="AB531" s="20"/>
     </row>
-    <row r="532" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA532" s="20"/>
       <c r="AB532" s="20"/>
     </row>
-    <row r="533" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA533" s="20"/>
       <c r="AB533" s="20"/>
     </row>
-    <row r="534" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA534" s="20"/>
       <c r="AB534" s="20"/>
     </row>
-    <row r="535" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA535" s="20"/>
       <c r="AB535" s="20"/>
     </row>
-    <row r="536" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA536" s="20"/>
       <c r="AB536" s="20"/>
     </row>
-    <row r="537" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA537" s="20"/>
       <c r="AB537" s="20"/>
     </row>
-    <row r="538" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA538" s="20"/>
       <c r="AB538" s="20"/>
     </row>
-    <row r="539" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA539" s="20"/>
       <c r="AB539" s="20"/>
     </row>
-    <row r="540" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA540" s="20"/>
       <c r="AB540" s="20"/>
     </row>
-    <row r="541" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA541" s="20"/>
       <c r="AB541" s="20"/>
     </row>
-    <row r="542" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA542" s="20"/>
       <c r="AB542" s="20"/>
     </row>
-    <row r="543" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA543" s="20"/>
       <c r="AB543" s="20"/>
     </row>
-    <row r="544" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA544" s="20"/>
       <c r="AB544" s="20"/>
     </row>
-    <row r="545" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA545" s="20"/>
       <c r="AB545" s="20"/>
     </row>
-    <row r="546" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA546" s="20"/>
       <c r="AB546" s="20"/>
     </row>
-    <row r="547" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA547" s="20"/>
       <c r="AB547" s="20"/>
     </row>
-    <row r="548" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA548" s="20"/>
       <c r="AB548" s="20"/>
     </row>
-    <row r="549" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA549" s="20"/>
       <c r="AB549" s="20"/>
     </row>
-    <row r="550" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA550" s="20"/>
       <c r="AB550" s="20"/>
     </row>
-    <row r="551" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA551" s="20"/>
       <c r="AB551" s="20"/>
     </row>
-    <row r="552" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA552" s="20"/>
       <c r="AB552" s="20"/>
     </row>
-    <row r="553" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA553" s="20"/>
       <c r="AB553" s="20"/>
     </row>
-    <row r="554" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA554" s="20"/>
       <c r="AB554" s="20"/>
     </row>
-    <row r="555" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA555" s="20"/>
       <c r="AB555" s="20"/>
     </row>
-    <row r="556" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA556" s="20"/>
       <c r="AB556" s="20"/>
     </row>
-    <row r="557" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA557" s="20"/>
       <c r="AB557" s="20"/>
     </row>
-    <row r="558" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA558" s="20"/>
       <c r="AB558" s="20"/>
     </row>
-    <row r="559" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA559" s="20"/>
       <c r="AB559" s="20"/>
     </row>
-    <row r="560" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA560" s="20"/>
       <c r="AB560" s="20"/>
     </row>
-    <row r="561" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA561" s="20"/>
       <c r="AB561" s="20"/>
     </row>
-    <row r="562" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA562" s="20"/>
       <c r="AB562" s="20"/>
     </row>
-    <row r="563" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA563" s="20"/>
       <c r="AB563" s="20"/>
     </row>
-    <row r="564" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA564" s="20"/>
       <c r="AB564" s="20"/>
     </row>
-    <row r="565" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA565" s="20"/>
       <c r="AB565" s="20"/>
     </row>
-    <row r="566" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA566" s="20"/>
       <c r="AB566" s="20"/>
     </row>
-    <row r="567" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA567" s="20"/>
       <c r="AB567" s="20"/>
     </row>
-    <row r="568" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA568" s="20"/>
       <c r="AB568" s="20"/>
     </row>
-    <row r="569" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA569" s="20"/>
       <c r="AB569" s="20"/>
     </row>
-    <row r="570" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA570" s="20"/>
       <c r="AB570" s="20"/>
     </row>
-    <row r="571" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA571" s="20"/>
       <c r="AB571" s="20"/>
     </row>
-    <row r="572" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA572" s="20"/>
       <c r="AB572" s="20"/>
     </row>
-    <row r="573" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA573" s="20"/>
       <c r="AB573" s="20"/>
     </row>
-    <row r="574" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA574" s="20"/>
       <c r="AB574" s="20"/>
     </row>
-    <row r="575" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA575" s="20"/>
       <c r="AB575" s="20"/>
     </row>
-    <row r="576" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA576" s="20"/>
       <c r="AB576" s="20"/>
     </row>
-    <row r="577" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA577" s="20"/>
       <c r="AB577" s="20"/>
     </row>
-    <row r="578" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA578" s="20"/>
       <c r="AB578" s="20"/>
     </row>
-    <row r="579" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA579" s="20"/>
       <c r="AB579" s="20"/>
     </row>
-    <row r="580" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA580" s="20"/>
       <c r="AB580" s="20"/>
     </row>
-    <row r="581" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA581" s="20"/>
       <c r="AB581" s="20"/>
     </row>
-    <row r="582" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA582" s="20"/>
       <c r="AB582" s="20"/>
     </row>
-    <row r="583" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA583" s="20"/>
       <c r="AB583" s="20"/>
     </row>
-    <row r="584" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA584" s="20"/>
       <c r="AB584" s="20"/>
     </row>
-    <row r="585" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA585" s="20"/>
       <c r="AB585" s="20"/>
     </row>
-    <row r="586" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA586" s="20"/>
       <c r="AB586" s="20"/>
     </row>
-    <row r="587" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA587" s="20"/>
       <c r="AB587" s="20"/>
     </row>
-    <row r="588" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA588" s="20"/>
       <c r="AB588" s="20"/>
     </row>
-    <row r="589" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA589" s="20"/>
       <c r="AB589" s="20"/>
     </row>
-    <row r="590" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA590" s="20"/>
       <c r="AB590" s="20"/>
     </row>
-    <row r="591" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA591" s="20"/>
       <c r="AB591" s="20"/>
     </row>
-    <row r="592" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA592" s="20"/>
       <c r="AB592" s="20"/>
     </row>
-    <row r="593" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA593" s="20"/>
       <c r="AB593" s="20"/>
     </row>
-    <row r="594" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA594" s="20"/>
       <c r="AB594" s="20"/>
     </row>
-    <row r="595" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA595" s="20"/>
       <c r="AB595" s="20"/>
     </row>
-    <row r="596" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA596" s="20"/>
       <c r="AB596" s="20"/>
     </row>
-    <row r="597" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA597" s="20"/>
       <c r="AB597" s="20"/>
     </row>
-    <row r="598" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA598" s="20"/>
       <c r="AB598" s="20"/>
     </row>
-    <row r="599" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA599" s="20"/>
       <c r="AB599" s="20"/>
     </row>
-    <row r="600" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA600" s="20"/>
       <c r="AB600" s="20"/>
     </row>
-    <row r="601" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA601" s="20"/>
       <c r="AB601" s="20"/>
     </row>
-    <row r="602" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA602" s="20"/>
       <c r="AB602" s="20"/>
     </row>
-    <row r="603" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA603" s="20"/>
       <c r="AB603" s="20"/>
     </row>
-    <row r="604" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA604" s="20"/>
       <c r="AB604" s="20"/>
     </row>
-    <row r="605" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA605" s="20"/>
       <c r="AB605" s="20"/>
     </row>
-    <row r="606" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA606" s="20"/>
       <c r="AB606" s="20"/>
     </row>
-    <row r="607" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA607" s="20"/>
       <c r="AB607" s="20"/>
     </row>
-    <row r="608" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA608" s="20"/>
       <c r="AB608" s="20"/>
     </row>
-    <row r="609" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA609" s="20"/>
       <c r="AB609" s="20"/>
     </row>
-    <row r="610" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA610" s="20"/>
       <c r="AB610" s="20"/>
     </row>
-    <row r="611" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA611" s="20"/>
       <c r="AB611" s="20"/>
     </row>
-    <row r="612" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA612" s="20"/>
       <c r="AB612" s="20"/>
     </row>
-    <row r="613" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA613" s="20"/>
       <c r="AB613" s="20"/>
     </row>
-    <row r="614" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA614" s="20"/>
       <c r="AB614" s="20"/>
     </row>
-    <row r="615" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA615" s="20"/>
       <c r="AB615" s="20"/>
     </row>
-    <row r="616" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA616" s="20"/>
       <c r="AB616" s="20"/>
     </row>
-    <row r="617" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA617" s="20"/>
       <c r="AB617" s="20"/>
     </row>
-    <row r="618" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA618" s="20"/>
       <c r="AB618" s="20"/>
     </row>
-    <row r="619" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA619" s="20"/>
       <c r="AB619" s="20"/>
     </row>
-    <row r="620" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA620" s="20"/>
       <c r="AB620" s="20"/>
     </row>
-    <row r="621" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA621" s="20"/>
       <c r="AB621" s="20"/>
     </row>
-    <row r="622" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA622" s="20"/>
       <c r="AB622" s="20"/>
     </row>
-    <row r="623" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA623" s="20"/>
       <c r="AB623" s="20"/>
     </row>
-    <row r="624" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA624" s="20"/>
       <c r="AB624" s="20"/>
     </row>
-    <row r="625" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA625" s="20"/>
       <c r="AB625" s="20"/>
     </row>
-    <row r="626" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA626" s="20"/>
       <c r="AB626" s="20"/>
     </row>
-    <row r="627" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA627" s="20"/>
       <c r="AB627" s="20"/>
     </row>
-    <row r="628" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA628" s="20"/>
       <c r="AB628" s="20"/>
     </row>
-    <row r="629" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA629" s="20"/>
       <c r="AB629" s="20"/>
     </row>
-    <row r="630" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA630" s="20"/>
       <c r="AB630" s="20"/>
     </row>
-    <row r="631" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA631" s="20"/>
       <c r="AB631" s="20"/>
     </row>
-    <row r="632" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA632" s="20"/>
       <c r="AB632" s="20"/>
     </row>
-    <row r="633" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA633" s="20"/>
       <c r="AB633" s="20"/>
     </row>
-    <row r="634" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA634" s="20"/>
       <c r="AB634" s="20"/>
     </row>
-    <row r="635" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA635" s="20"/>
       <c r="AB635" s="20"/>
     </row>
-    <row r="636" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA636" s="20"/>
       <c r="AB636" s="20"/>
     </row>
-    <row r="637" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA637" s="20"/>
       <c r="AB637" s="20"/>
     </row>
-    <row r="638" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA638" s="20"/>
       <c r="AB638" s="20"/>
     </row>
-    <row r="639" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA639" s="20"/>
       <c r="AB639" s="20"/>
     </row>
-    <row r="640" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA640" s="20"/>
       <c r="AB640" s="20"/>
     </row>
-    <row r="641" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA641" s="20"/>
       <c r="AB641" s="20"/>
     </row>
-    <row r="642" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA642" s="20"/>
       <c r="AB642" s="20"/>
     </row>
-    <row r="643" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA643" s="20"/>
       <c r="AB643" s="20"/>
     </row>
-    <row r="644" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA644" s="20"/>
       <c r="AB644" s="20"/>
     </row>
-    <row r="645" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA645" s="20"/>
       <c r="AB645" s="20"/>
     </row>
-    <row r="646" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA646" s="20"/>
       <c r="AB646" s="20"/>
     </row>
-    <row r="647" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA647" s="20"/>
       <c r="AB647" s="20"/>
     </row>
-    <row r="648" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA648" s="20"/>
       <c r="AB648" s="20"/>
     </row>
-    <row r="649" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA649" s="20"/>
       <c r="AB649" s="20"/>
     </row>
-    <row r="650" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA650" s="20"/>
       <c r="AB650" s="20"/>
     </row>
-    <row r="651" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA651" s="20"/>
       <c r="AB651" s="20"/>
     </row>
-    <row r="652" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA652" s="20"/>
       <c r="AB652" s="20"/>
     </row>
-    <row r="653" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA653" s="20"/>
       <c r="AB653" s="20"/>
     </row>
-    <row r="654" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA654" s="20"/>
       <c r="AB654" s="20"/>
     </row>
-    <row r="655" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA655" s="20"/>
       <c r="AB655" s="20"/>
     </row>
-    <row r="656" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA656" s="20"/>
       <c r="AB656" s="20"/>
     </row>
-    <row r="657" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA657" s="20"/>
       <c r="AB657" s="20"/>
     </row>
-    <row r="658" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA658" s="20"/>
       <c r="AB658" s="20"/>
     </row>
-    <row r="659" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA659" s="20"/>
       <c r="AB659" s="20"/>
     </row>
-    <row r="660" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA660" s="20"/>
       <c r="AB660" s="20"/>
     </row>
-    <row r="661" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA661" s="20"/>
       <c r="AB661" s="20"/>
     </row>
-    <row r="662" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA662" s="20"/>
       <c r="AB662" s="20"/>
     </row>
-    <row r="663" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA663" s="20"/>
       <c r="AB663" s="20"/>
     </row>
-    <row r="664" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA664" s="20"/>
       <c r="AB664" s="20"/>
     </row>
-    <row r="665" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA665" s="20"/>
       <c r="AB665" s="20"/>
     </row>
-    <row r="666" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA666" s="20"/>
       <c r="AB666" s="20"/>
     </row>
-    <row r="667" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA667" s="20"/>
       <c r="AB667" s="20"/>
     </row>
-    <row r="668" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA668" s="20"/>
       <c r="AB668" s="20"/>
     </row>
-    <row r="669" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA669" s="20"/>
       <c r="AB669" s="20"/>
     </row>
-    <row r="670" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA670" s="20"/>
       <c r="AB670" s="20"/>
     </row>
-    <row r="671" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA671" s="20"/>
       <c r="AB671" s="20"/>
     </row>
-    <row r="672" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA672" s="20"/>
       <c r="AB672" s="20"/>
     </row>
-    <row r="673" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA673" s="20"/>
       <c r="AB673" s="20"/>
     </row>
-    <row r="674" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA674" s="20"/>
       <c r="AB674" s="20"/>
     </row>
-    <row r="675" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA675" s="20"/>
       <c r="AB675" s="20"/>
     </row>
-    <row r="676" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA676" s="20"/>
       <c r="AB676" s="20"/>
     </row>
-    <row r="677" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA677" s="20"/>
       <c r="AB677" s="20"/>
     </row>
-    <row r="678" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA678" s="20"/>
       <c r="AB678" s="20"/>
     </row>
-    <row r="679" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA679" s="20"/>
       <c r="AB679" s="20"/>
     </row>
-    <row r="680" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA680" s="20"/>
       <c r="AB680" s="20"/>
     </row>
-    <row r="681" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA681" s="20"/>
       <c r="AB681" s="20"/>
     </row>
-    <row r="682" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA682" s="20"/>
       <c r="AB682" s="20"/>
     </row>
-    <row r="683" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA683" s="20"/>
       <c r="AB683" s="20"/>
     </row>
-    <row r="684" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA684" s="20"/>
       <c r="AB684" s="20"/>
     </row>
-    <row r="685" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA685" s="20"/>
       <c r="AB685" s="20"/>
     </row>
-    <row r="686" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA686" s="20"/>
       <c r="AB686" s="20"/>
     </row>
-    <row r="687" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA687" s="20"/>
       <c r="AB687" s="20"/>
     </row>
-    <row r="688" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA688" s="20"/>
       <c r="AB688" s="20"/>
     </row>
-    <row r="689" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA689" s="20"/>
       <c r="AB689" s="20"/>
     </row>
-    <row r="690" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA690" s="20"/>
       <c r="AB690" s="20"/>
     </row>
-    <row r="691" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA691" s="20"/>
       <c r="AB691" s="20"/>
     </row>
-    <row r="692" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA692" s="20"/>
       <c r="AB692" s="20"/>
     </row>
-    <row r="693" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA693" s="20"/>
       <c r="AB693" s="20"/>
     </row>
-    <row r="694" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA694" s="20"/>
       <c r="AB694" s="20"/>
     </row>
-    <row r="695" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA695" s="20"/>
       <c r="AB695" s="20"/>
     </row>
-    <row r="696" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA696" s="20"/>
       <c r="AB696" s="20"/>
     </row>
-    <row r="697" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA697" s="20"/>
       <c r="AB697" s="20"/>
     </row>
-    <row r="698" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA698" s="20"/>
       <c r="AB698" s="20"/>
     </row>
-    <row r="699" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA699" s="20"/>
       <c r="AB699" s="20"/>
     </row>
-    <row r="700" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA700" s="20"/>
       <c r="AB700" s="20"/>
     </row>
-    <row r="701" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA701" s="20"/>
       <c r="AB701" s="20"/>
     </row>
-    <row r="702" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA702" s="20"/>
       <c r="AB702" s="20"/>
     </row>
-    <row r="703" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA703" s="20"/>
       <c r="AB703" s="20"/>
     </row>
-    <row r="704" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA704" s="20"/>
       <c r="AB704" s="20"/>
     </row>
-    <row r="705" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA705" s="20"/>
       <c r="AB705" s="20"/>
     </row>
-    <row r="706" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA706" s="20"/>
       <c r="AB706" s="20"/>
     </row>
-    <row r="707" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA707" s="20"/>
       <c r="AB707" s="20"/>
     </row>
-    <row r="708" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA708" s="20"/>
       <c r="AB708" s="20"/>
     </row>
-    <row r="709" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA709" s="20"/>
       <c r="AB709" s="20"/>
     </row>
-    <row r="710" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA710" s="20"/>
       <c r="AB710" s="20"/>
     </row>
-    <row r="711" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA711" s="20"/>
       <c r="AB711" s="20"/>
     </row>
-    <row r="712" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA712" s="20"/>
       <c r="AB712" s="20"/>
     </row>
-    <row r="713" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA713" s="20"/>
       <c r="AB713" s="20"/>
     </row>
-    <row r="714" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA714" s="20"/>
       <c r="AB714" s="20"/>
     </row>
-    <row r="715" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA715" s="20"/>
       <c r="AB715" s="20"/>
     </row>
-    <row r="716" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA716" s="20"/>
       <c r="AB716" s="20"/>
     </row>
-    <row r="717" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA717" s="20"/>
       <c r="AB717" s="20"/>
     </row>
-    <row r="718" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA718" s="20"/>
       <c r="AB718" s="20"/>
     </row>
-    <row r="719" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA719" s="20"/>
       <c r="AB719" s="20"/>
     </row>
-    <row r="720" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA720" s="20"/>
       <c r="AB720" s="20"/>
     </row>
-    <row r="721" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA721" s="20"/>
       <c r="AB721" s="20"/>
     </row>
-    <row r="722" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA722" s="20"/>
       <c r="AB722" s="20"/>
     </row>
-    <row r="723" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA723" s="20"/>
       <c r="AB723" s="20"/>
     </row>
-    <row r="724" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA724" s="20"/>
       <c r="AB724" s="20"/>
     </row>
-    <row r="725" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA725" s="20"/>
       <c r="AB725" s="20"/>
     </row>
-    <row r="726" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA726" s="20"/>
       <c r="AB726" s="20"/>
     </row>
-    <row r="727" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA727" s="20"/>
       <c r="AB727" s="20"/>
     </row>
-    <row r="728" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA728" s="20"/>
       <c r="AB728" s="20"/>
     </row>
-    <row r="729" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA729" s="20"/>
       <c r="AB729" s="20"/>
     </row>
-    <row r="730" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA730" s="20"/>
       <c r="AB730" s="20"/>
     </row>
-    <row r="731" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA731" s="20"/>
       <c r="AB731" s="20"/>
     </row>
-    <row r="732" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA732" s="20"/>
       <c r="AB732" s="20"/>
     </row>
-    <row r="733" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA733" s="20"/>
       <c r="AB733" s="20"/>
     </row>
-    <row r="734" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA734" s="20"/>
       <c r="AB734" s="20"/>
     </row>
-    <row r="735" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA735" s="20"/>
       <c r="AB735" s="20"/>
     </row>
-    <row r="736" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA736" s="20"/>
       <c r="AB736" s="20"/>
     </row>
-    <row r="737" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA737" s="20"/>
       <c r="AB737" s="20"/>
     </row>
-    <row r="738" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA738" s="20"/>
       <c r="AB738" s="20"/>
     </row>
-    <row r="739" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA739" s="20"/>
       <c r="AB739" s="20"/>
     </row>
-    <row r="740" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA740" s="20"/>
       <c r="AB740" s="20"/>
     </row>
-    <row r="741" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA741" s="20"/>
       <c r="AB741" s="20"/>
     </row>
-    <row r="742" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA742" s="20"/>
       <c r="AB742" s="20"/>
     </row>
-    <row r="743" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA743" s="20"/>
       <c r="AB743" s="20"/>
     </row>
-    <row r="744" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA744" s="20"/>
       <c r="AB744" s="20"/>
     </row>
-    <row r="745" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA745" s="20"/>
       <c r="AB745" s="20"/>
     </row>
-    <row r="746" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA746" s="20"/>
       <c r="AB746" s="20"/>
     </row>
-    <row r="747" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA747" s="20"/>
       <c r="AB747" s="20"/>
     </row>
-    <row r="748" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA748" s="20"/>
       <c r="AB748" s="20"/>
     </row>
-    <row r="749" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA749" s="20"/>
       <c r="AB749" s="20"/>
     </row>
-    <row r="750" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA750" s="20"/>
       <c r="AB750" s="20"/>
     </row>
-    <row r="751" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA751" s="20"/>
       <c r="AB751" s="20"/>
     </row>
-    <row r="752" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA752" s="20"/>
       <c r="AB752" s="20"/>
     </row>
-    <row r="753" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA753" s="20"/>
       <c r="AB753" s="20"/>
     </row>
-    <row r="754" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA754" s="20"/>
       <c r="AB754" s="20"/>
     </row>
-    <row r="755" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA755" s="20"/>
       <c r="AB755" s="20"/>
     </row>
-    <row r="756" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA756" s="20"/>
       <c r="AB756" s="20"/>
     </row>
-    <row r="757" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA757" s="20"/>
       <c r="AB757" s="20"/>
     </row>
-    <row r="758" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA758" s="20"/>
       <c r="AB758" s="20"/>
     </row>
-    <row r="759" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA759" s="20"/>
       <c r="AB759" s="20"/>
     </row>
-    <row r="760" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA760" s="20"/>
       <c r="AB760" s="20"/>
     </row>
-    <row r="761" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA761" s="20"/>
       <c r="AB761" s="20"/>
     </row>
-    <row r="762" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA762" s="20"/>
       <c r="AB762" s="20"/>
     </row>
-    <row r="763" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA763" s="20"/>
       <c r="AB763" s="20"/>
     </row>
-    <row r="764" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA764" s="20"/>
       <c r="AB764" s="20"/>
     </row>
-    <row r="765" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA765" s="20"/>
       <c r="AB765" s="20"/>
     </row>
-    <row r="766" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA766" s="20"/>
       <c r="AB766" s="20"/>
     </row>
-    <row r="767" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA767" s="20"/>
       <c r="AB767" s="20"/>
     </row>
-    <row r="768" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA768" s="20"/>
       <c r="AB768" s="20"/>
     </row>
-    <row r="769" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA769" s="20"/>
       <c r="AB769" s="20"/>
     </row>
-    <row r="770" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA770" s="20"/>
       <c r="AB770" s="20"/>
     </row>
-    <row r="771" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA771" s="20"/>
       <c r="AB771" s="20"/>
     </row>
-    <row r="772" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA772" s="20"/>
       <c r="AB772" s="20"/>
     </row>
-    <row r="773" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA773" s="20"/>
       <c r="AB773" s="20"/>
     </row>
-    <row r="774" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA774" s="20"/>
       <c r="AB774" s="20"/>
     </row>
-    <row r="775" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA775" s="20"/>
       <c r="AB775" s="20"/>
     </row>
-    <row r="776" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA776" s="20"/>
       <c r="AB776" s="20"/>
     </row>
-    <row r="777" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA777" s="20"/>
       <c r="AB777" s="20"/>
     </row>
-    <row r="778" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA778" s="20"/>
       <c r="AB778" s="20"/>
     </row>
-    <row r="779" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA779" s="20"/>
       <c r="AB779" s="20"/>
     </row>
-    <row r="780" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA780" s="20"/>
       <c r="AB780" s="20"/>
     </row>
-    <row r="781" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA781" s="20"/>
       <c r="AB781" s="20"/>
     </row>
-    <row r="782" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA782" s="20"/>
       <c r="AB782" s="20"/>
     </row>
-    <row r="783" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA783" s="20"/>
       <c r="AB783" s="20"/>
     </row>
-    <row r="784" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA784" s="20"/>
       <c r="AB784" s="20"/>
     </row>
-    <row r="785" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA785" s="20"/>
       <c r="AB785" s="20"/>
     </row>
-    <row r="786" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA786" s="20"/>
       <c r="AB786" s="20"/>
     </row>
-    <row r="787" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA787" s="20"/>
       <c r="AB787" s="20"/>
     </row>
-    <row r="788" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA788" s="20"/>
       <c r="AB788" s="20"/>
     </row>
-    <row r="789" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA789" s="20"/>
       <c r="AB789" s="20"/>
     </row>
-    <row r="790" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA790" s="20"/>
       <c r="AB790" s="20"/>
     </row>
-    <row r="791" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA791" s="20"/>
       <c r="AB791" s="20"/>
     </row>
-    <row r="792" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA792" s="20"/>
       <c r="AB792" s="20"/>
     </row>
-    <row r="793" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA793" s="20"/>
       <c r="AB793" s="20"/>
     </row>
-    <row r="794" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA794" s="20"/>
       <c r="AB794" s="20"/>
     </row>
-    <row r="795" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA795" s="20"/>
       <c r="AB795" s="20"/>
     </row>
-    <row r="796" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA796" s="20"/>
       <c r="AB796" s="20"/>
     </row>
-    <row r="797" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA797" s="20"/>
       <c r="AB797" s="20"/>
     </row>
-    <row r="798" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA798" s="20"/>
       <c r="AB798" s="20"/>
     </row>
-    <row r="799" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA799" s="20"/>
       <c r="AB799" s="20"/>
     </row>
-    <row r="800" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA800" s="20"/>
       <c r="AB800" s="20"/>
     </row>
-    <row r="801" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA801" s="20"/>
       <c r="AB801" s="20"/>
     </row>
-    <row r="802" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA802" s="20"/>
       <c r="AB802" s="20"/>
     </row>
-    <row r="803" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA803" s="20"/>
       <c r="AB803" s="20"/>
     </row>
-    <row r="804" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA804" s="20"/>
       <c r="AB804" s="20"/>
     </row>
-    <row r="805" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA805" s="20"/>
       <c r="AB805" s="20"/>
     </row>
-    <row r="806" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA806" s="20"/>
       <c r="AB806" s="20"/>
     </row>
-    <row r="807" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA807" s="20"/>
       <c r="AB807" s="20"/>
     </row>
-    <row r="808" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA808" s="20"/>
       <c r="AB808" s="20"/>
     </row>
-    <row r="809" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA809" s="20"/>
       <c r="AB809" s="20"/>
     </row>
-    <row r="810" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA810" s="20"/>
       <c r="AB810" s="20"/>
     </row>
-    <row r="811" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA811" s="20"/>
       <c r="AB811" s="20"/>
     </row>
-    <row r="812" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA812" s="20"/>
       <c r="AB812" s="20"/>
     </row>
-    <row r="813" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA813" s="20"/>
       <c r="AB813" s="20"/>
     </row>
-    <row r="814" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA814" s="20"/>
       <c r="AB814" s="20"/>
     </row>
-    <row r="815" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA815" s="20"/>
       <c r="AB815" s="20"/>
     </row>
-    <row r="816" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA816" s="20"/>
       <c r="AB816" s="20"/>
     </row>
-    <row r="817" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA817" s="20"/>
       <c r="AB817" s="20"/>
     </row>
-    <row r="818" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA818" s="20"/>
       <c r="AB818" s="20"/>
     </row>
-    <row r="819" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA819" s="20"/>
       <c r="AB819" s="20"/>
     </row>
-    <row r="820" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA820" s="20"/>
       <c r="AB820" s="20"/>
     </row>
-    <row r="821" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA821" s="20"/>
       <c r="AB821" s="20"/>
     </row>
-    <row r="822" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA822" s="20"/>
       <c r="AB822" s="20"/>
     </row>
-    <row r="823" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA823" s="20"/>
       <c r="AB823" s="20"/>
     </row>
-    <row r="824" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA824" s="20"/>
       <c r="AB824" s="20"/>
     </row>
-    <row r="825" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA825" s="20"/>
       <c r="AB825" s="20"/>
     </row>
-    <row r="826" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA826" s="20"/>
       <c r="AB826" s="20"/>
     </row>
-    <row r="827" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA827" s="20"/>
       <c r="AB827" s="20"/>
     </row>
-    <row r="828" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA828" s="20"/>
       <c r="AB828" s="20"/>
     </row>
-    <row r="829" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA829" s="20"/>
       <c r="AB829" s="20"/>
     </row>
-    <row r="830" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA830" s="20"/>
       <c r="AB830" s="20"/>
     </row>
-    <row r="831" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA831" s="20"/>
       <c r="AB831" s="20"/>
     </row>
-    <row r="832" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA832" s="20"/>
       <c r="AB832" s="20"/>
     </row>
-    <row r="833" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA833" s="20"/>
       <c r="AB833" s="20"/>
     </row>
-    <row r="834" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA834" s="20"/>
       <c r="AB834" s="20"/>
     </row>
-    <row r="835" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA835" s="20"/>
       <c r="AB835" s="20"/>
     </row>
-    <row r="836" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA836" s="20"/>
       <c r="AB836" s="20"/>
     </row>
-    <row r="837" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA837" s="20"/>
       <c r="AB837" s="20"/>
     </row>
-    <row r="838" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA838" s="20"/>
       <c r="AB838" s="20"/>
     </row>
-    <row r="839" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA839" s="20"/>
       <c r="AB839" s="20"/>
     </row>
-    <row r="840" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA840" s="20"/>
       <c r="AB840" s="20"/>
     </row>
-    <row r="841" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA841" s="20"/>
       <c r="AB841" s="20"/>
     </row>
-    <row r="842" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA842" s="20"/>
       <c r="AB842" s="20"/>
     </row>
-    <row r="843" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA843" s="20"/>
       <c r="AB843" s="20"/>
     </row>
-    <row r="844" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA844" s="20"/>
       <c r="AB844" s="20"/>
     </row>
-    <row r="845" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA845" s="20"/>
       <c r="AB845" s="20"/>
     </row>
-    <row r="846" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA846" s="20"/>
       <c r="AB846" s="20"/>
     </row>
-    <row r="847" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA847" s="20"/>
       <c r="AB847" s="20"/>
     </row>
-    <row r="848" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA848" s="20"/>
       <c r="AB848" s="20"/>
     </row>
-    <row r="849" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA849" s="20"/>
       <c r="AB849" s="20"/>
     </row>
-    <row r="850" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA850" s="20"/>
       <c r="AB850" s="20"/>
     </row>
-    <row r="851" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA851" s="20"/>
       <c r="AB851" s="20"/>
     </row>
-    <row r="852" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA852" s="20"/>
       <c r="AB852" s="20"/>
     </row>
-    <row r="853" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA853" s="20"/>
       <c r="AB853" s="20"/>
     </row>
-    <row r="854" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA854" s="20"/>
       <c r="AB854" s="20"/>
     </row>
-    <row r="855" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA855" s="20"/>
       <c r="AB855" s="20"/>
     </row>
-    <row r="856" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA856" s="20"/>
       <c r="AB856" s="20"/>
     </row>
-    <row r="857" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA857" s="20"/>
       <c r="AB857" s="20"/>
     </row>
-    <row r="858" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA858" s="20"/>
       <c r="AB858" s="20"/>
     </row>
-    <row r="859" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA859" s="20"/>
       <c r="AB859" s="20"/>
     </row>
-    <row r="860" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA860" s="20"/>
       <c r="AB860" s="20"/>
     </row>
-    <row r="861" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA861" s="20"/>
       <c r="AB861" s="20"/>
     </row>
-    <row r="862" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA862" s="20"/>
       <c r="AB862" s="20"/>
     </row>
-    <row r="863" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA863" s="20"/>
       <c r="AB863" s="20"/>
     </row>
-    <row r="864" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA864" s="20"/>
       <c r="AB864" s="20"/>
     </row>
-    <row r="865" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA865" s="20"/>
       <c r="AB865" s="20"/>
     </row>
-    <row r="866" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA866" s="20"/>
       <c r="AB866" s="20"/>
     </row>
-    <row r="867" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA867" s="20"/>
       <c r="AB867" s="20"/>
     </row>
-    <row r="868" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA868" s="20"/>
       <c r="AB868" s="20"/>
     </row>
-    <row r="869" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA869" s="20"/>
       <c r="AB869" s="20"/>
     </row>
-    <row r="870" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA870" s="20"/>
       <c r="AB870" s="20"/>
     </row>
-    <row r="871" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA871" s="20"/>
       <c r="AB871" s="20"/>
     </row>
-    <row r="872" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA872" s="20"/>
       <c r="AB872" s="20"/>
     </row>
-    <row r="873" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA873" s="20"/>
       <c r="AB873" s="20"/>
     </row>
-    <row r="874" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA874" s="20"/>
       <c r="AB874" s="20"/>
     </row>
-    <row r="875" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA875" s="20"/>
       <c r="AB875" s="20"/>
     </row>
-    <row r="876" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA876" s="20"/>
       <c r="AB876" s="20"/>
     </row>
-    <row r="877" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA877" s="20"/>
       <c r="AB877" s="20"/>
     </row>
-    <row r="878" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA878" s="20"/>
       <c r="AB878" s="20"/>
     </row>
-    <row r="879" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA879" s="20"/>
       <c r="AB879" s="20"/>
     </row>
-    <row r="880" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA880" s="20"/>
       <c r="AB880" s="20"/>
     </row>
-    <row r="881" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA881" s="20"/>
       <c r="AB881" s="20"/>
     </row>
-    <row r="882" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA882" s="20"/>
       <c r="AB882" s="20"/>
     </row>
-    <row r="883" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA883" s="20"/>
       <c r="AB883" s="20"/>
     </row>
-    <row r="884" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA884" s="20"/>
       <c r="AB884" s="20"/>
     </row>
-    <row r="885" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA885" s="20"/>
       <c r="AB885" s="20"/>
     </row>
-    <row r="886" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA886" s="20"/>
       <c r="AB886" s="20"/>
     </row>
-    <row r="887" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA887" s="20"/>
       <c r="AB887" s="20"/>
     </row>
-    <row r="888" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA888" s="20"/>
       <c r="AB888" s="20"/>
     </row>
-    <row r="889" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA889" s="20"/>
       <c r="AB889" s="20"/>
     </row>
-    <row r="890" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA890" s="20"/>
       <c r="AB890" s="20"/>
     </row>
-    <row r="891" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA891" s="20"/>
       <c r="AB891" s="20"/>
     </row>
-    <row r="892" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA892" s="20"/>
       <c r="AB892" s="20"/>
     </row>
-    <row r="893" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA893" s="20"/>
       <c r="AB893" s="20"/>
     </row>
-    <row r="894" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA894" s="20"/>
       <c r="AB894" s="20"/>
     </row>
-    <row r="895" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA895" s="20"/>
       <c r="AB895" s="20"/>
     </row>
-    <row r="896" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA896" s="20"/>
       <c r="AB896" s="20"/>
     </row>
-    <row r="897" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA897" s="20"/>
       <c r="AB897" s="20"/>
     </row>
-    <row r="898" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA898" s="20"/>
       <c r="AB898" s="20"/>
     </row>
-    <row r="899" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA899" s="20"/>
       <c r="AB899" s="20"/>
     </row>
-    <row r="900" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA900" s="20"/>
       <c r="AB900" s="20"/>
     </row>
-    <row r="901" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA901" s="20"/>
       <c r="AB901" s="20"/>
     </row>
-    <row r="902" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA902" s="20"/>
       <c r="AB902" s="20"/>
     </row>
-    <row r="903" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA903" s="20"/>
       <c r="AB903" s="20"/>
     </row>
-    <row r="904" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA904" s="20"/>
       <c r="AB904" s="20"/>
     </row>
-    <row r="905" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA905" s="20"/>
       <c r="AB905" s="20"/>
     </row>
-    <row r="906" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA906" s="20"/>
       <c r="AB906" s="20"/>
     </row>
-    <row r="907" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA907" s="20"/>
       <c r="AB907" s="20"/>
     </row>
-    <row r="908" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA908" s="20"/>
       <c r="AB908" s="20"/>
     </row>
-    <row r="909" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA909" s="20"/>
       <c r="AB909" s="20"/>
     </row>
-    <row r="910" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA910" s="20"/>
       <c r="AB910" s="20"/>
     </row>
-    <row r="911" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA911" s="20"/>
       <c r="AB911" s="20"/>
     </row>
-    <row r="912" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA912" s="20"/>
       <c r="AB912" s="20"/>
     </row>
-    <row r="913" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA913" s="20"/>
       <c r="AB913" s="20"/>
     </row>
-    <row r="914" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA914" s="20"/>
       <c r="AB914" s="20"/>
     </row>
-    <row r="915" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA915" s="20"/>
       <c r="AB915" s="20"/>
     </row>
-    <row r="916" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA916" s="20"/>
       <c r="AB916" s="20"/>
     </row>
-    <row r="917" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA917" s="20"/>
       <c r="AB917" s="20"/>
     </row>
-    <row r="918" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA918" s="20"/>
       <c r="AB918" s="20"/>
     </row>
-    <row r="919" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA919" s="20"/>
       <c r="AB919" s="20"/>
     </row>
-    <row r="920" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA920" s="20"/>
       <c r="AB920" s="20"/>
     </row>
-    <row r="921" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA921" s="20"/>
       <c r="AB921" s="20"/>
     </row>
-    <row r="922" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA922" s="20"/>
       <c r="AB922" s="20"/>
     </row>
-    <row r="923" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA923" s="20"/>
       <c r="AB923" s="20"/>
     </row>
-    <row r="924" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA924" s="20"/>
       <c r="AB924" s="20"/>
     </row>
-    <row r="925" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA925" s="20"/>
       <c r="AB925" s="20"/>
     </row>
-    <row r="926" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA926" s="20"/>
       <c r="AB926" s="20"/>
     </row>
-    <row r="927" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA927" s="20"/>
       <c r="AB927" s="20"/>
     </row>
-    <row r="928" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA928" s="20"/>
       <c r="AB928" s="20"/>
     </row>
-    <row r="929" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA929" s="20"/>
       <c r="AB929" s="20"/>
     </row>
-    <row r="930" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA930" s="20"/>
       <c r="AB930" s="20"/>
     </row>
-    <row r="931" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA931" s="20"/>
       <c r="AB931" s="20"/>
     </row>
-    <row r="932" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA932" s="20"/>
       <c r="AB932" s="20"/>
     </row>
-    <row r="933" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA933" s="20"/>
       <c r="AB933" s="20"/>
     </row>
-    <row r="934" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA934" s="20"/>
       <c r="AB934" s="20"/>
     </row>
-    <row r="935" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA935" s="20"/>
       <c r="AB935" s="20"/>
     </row>
-    <row r="936" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA936" s="20"/>
       <c r="AB936" s="20"/>
     </row>
-    <row r="937" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA937" s="20"/>
       <c r="AB937" s="20"/>
     </row>
-    <row r="938" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA938" s="20"/>
       <c r="AB938" s="20"/>
     </row>
-    <row r="939" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA939" s="20"/>
       <c r="AB939" s="20"/>
     </row>
-    <row r="940" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA940" s="20"/>
       <c r="AB940" s="20"/>
     </row>
-    <row r="941" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA941" s="20"/>
       <c r="AB941" s="20"/>
     </row>
-    <row r="942" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA942" s="20"/>
       <c r="AB942" s="20"/>
     </row>
-    <row r="943" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA943" s="20"/>
       <c r="AB943" s="20"/>
     </row>
-    <row r="944" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA944" s="20"/>
       <c r="AB944" s="20"/>
     </row>
-    <row r="945" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA945" s="20"/>
       <c r="AB945" s="20"/>
     </row>
-    <row r="946" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA946" s="20"/>
       <c r="AB946" s="20"/>
     </row>
-    <row r="947" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA947" s="20"/>
       <c r="AB947" s="20"/>
     </row>
-    <row r="948" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA948" s="20"/>
       <c r="AB948" s="20"/>
     </row>
-    <row r="949" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA949" s="20"/>
       <c r="AB949" s="20"/>
     </row>
-    <row r="950" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA950" s="20"/>
       <c r="AB950" s="20"/>
     </row>
-    <row r="951" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA951" s="20"/>
       <c r="AB951" s="20"/>
     </row>
-    <row r="952" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA952" s="20"/>
       <c r="AB952" s="20"/>
     </row>
-    <row r="953" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA953" s="20"/>
       <c r="AB953" s="20"/>
     </row>
-    <row r="954" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA954" s="20"/>
       <c r="AB954" s="20"/>
     </row>
-    <row r="955" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA955" s="20"/>
       <c r="AB955" s="20"/>
     </row>
-    <row r="956" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA956" s="20"/>
       <c r="AB956" s="20"/>
     </row>
-    <row r="957" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA957" s="20"/>
       <c r="AB957" s="20"/>
     </row>
-    <row r="958" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA958" s="20"/>
       <c r="AB958" s="20"/>
     </row>
-    <row r="959" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA959" s="20"/>
       <c r="AB959" s="20"/>
     </row>
-    <row r="960" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA960" s="20"/>
       <c r="AB960" s="20"/>
     </row>
-    <row r="961" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA961" s="20"/>
       <c r="AB961" s="20"/>
     </row>
-    <row r="962" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA962" s="20"/>
       <c r="AB962" s="20"/>
     </row>
-    <row r="963" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA963" s="20"/>
       <c r="AB963" s="20"/>
     </row>
-    <row r="964" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA964" s="20"/>
       <c r="AB964" s="20"/>
     </row>
-    <row r="965" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA965" s="20"/>
       <c r="AB965" s="20"/>
     </row>
-    <row r="966" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA966" s="20"/>
       <c r="AB966" s="20"/>
     </row>
-    <row r="967" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA967" s="20"/>
       <c r="AB967" s="20"/>
     </row>
-    <row r="968" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA968" s="20"/>
       <c r="AB968" s="20"/>
     </row>
-    <row r="969" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA969" s="20"/>
       <c r="AB969" s="20"/>
     </row>
-    <row r="970" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA970" s="20"/>
       <c r="AB970" s="20"/>
     </row>
-    <row r="971" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA971" s="20"/>
       <c r="AB971" s="20"/>
     </row>
-    <row r="972" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA972" s="20"/>
       <c r="AB972" s="20"/>
     </row>
-    <row r="973" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA973" s="20"/>
       <c r="AB973" s="20"/>
     </row>
-    <row r="974" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA974" s="20"/>
       <c r="AB974" s="20"/>
     </row>
-    <row r="975" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA975" s="20"/>
       <c r="AB975" s="20"/>
     </row>
-    <row r="976" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA976" s="20"/>
       <c r="AB976" s="20"/>
     </row>
-    <row r="977" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA977" s="20"/>
       <c r="AB977" s="20"/>
     </row>
-    <row r="978" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA978" s="20"/>
       <c r="AB978" s="20"/>
     </row>
-    <row r="979" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA979" s="20"/>
       <c r="AB979" s="20"/>
     </row>
-    <row r="980" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA980" s="20"/>
       <c r="AB980" s="20"/>
     </row>
-    <row r="981" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA981" s="20"/>
       <c r="AB981" s="20"/>
     </row>
-    <row r="982" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA982" s="20"/>
       <c r="AB982" s="20"/>
     </row>
-    <row r="983" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA983" s="20"/>
       <c r="AB983" s="20"/>
     </row>
-    <row r="984" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA984" s="20"/>
       <c r="AB984" s="20"/>
     </row>
-    <row r="985" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA985" s="20"/>
       <c r="AB985" s="20"/>
     </row>
-    <row r="986" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA986" s="20"/>
       <c r="AB986" s="20"/>
     </row>
-    <row r="987" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA987" s="20"/>
       <c r="AB987" s="20"/>
     </row>
-    <row r="988" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA988" s="20"/>
       <c r="AB988" s="20"/>
     </row>
-    <row r="989" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA989" s="20"/>
       <c r="AB989" s="20"/>
     </row>
-    <row r="990" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA990" s="20"/>
       <c r="AB990" s="20"/>
     </row>
-    <row r="991" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA991" s="20"/>
       <c r="AB991" s="20"/>
     </row>
-    <row r="992" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA992" s="20"/>
       <c r="AB992" s="20"/>
     </row>
-    <row r="993" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA993" s="20"/>
       <c r="AB993" s="20"/>
     </row>
-    <row r="994" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA994" s="20"/>
       <c r="AB994" s="20"/>
     </row>
-    <row r="995" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA995" s="20"/>
       <c r="AB995" s="20"/>
     </row>
-    <row r="996" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA996" s="20"/>
       <c r="AB996" s="20"/>
     </row>
-    <row r="997" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA997" s="20"/>
       <c r="AB997" s="20"/>
     </row>
-    <row r="998" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA998" s="20"/>
       <c r="AB998" s="20"/>
     </row>
-    <row r="999" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA999" s="20"/>
       <c r="AB999" s="20"/>
     </row>
-    <row r="1000" spans="27:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="27:28" ht="12.75" customHeight="1">
       <c r="AA1000" s="20"/>
       <c r="AB1000" s="20"/>
     </row>

--- a/resources/progetti_ottobre_2025_finale.xlsx
+++ b/resources/progetti_ottobre_2025_finale.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giacomoterreni/projects/homestead7/citizen/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3A9377-EDF6-9C47-8890-6ABF2C651954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1CDF8C-74B9-EB41-A247-724E00BF8549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8840" yWindow="3080" windowWidth="46000" windowHeight="19920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="63500" yWindow="1960" windowWidth="46000" windowHeight="19920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Risposte del modulo 1" sheetId="1" r:id="rId1"/>
     <sheet name="Foglio1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="273">
   <si>
     <t>Nr</t>
   </si>
@@ -1005,6 +1005,51 @@
   </si>
   <si>
     <t xml:space="preserve">Università degli Studi di Sassari </t>
+  </si>
+  <si>
+    <t>Simonetta Bagella</t>
+  </si>
+  <si>
+    <t>Lucio Bonato</t>
+  </si>
+  <si>
+    <t>Alessandro Nota</t>
+  </si>
+  <si>
+    <t>Marco Signore</t>
+  </si>
+  <si>
+    <t>Alessandro Campanaro</t>
+  </si>
+  <si>
+    <t>Ivo Rossetti</t>
+  </si>
+  <si>
+    <t>Fernando Rubino</t>
+  </si>
+  <si>
+    <t>Simona Bonelli</t>
+  </si>
+  <si>
+    <t>Raffaella Bullo</t>
+  </si>
+  <si>
+    <t>Lara Maistrello</t>
+  </si>
+  <si>
+    <t>Alessio Polvani</t>
+  </si>
+  <si>
+    <t>Due Project</t>
+  </si>
+  <si>
+    <t>Debora Barbato</t>
+  </si>
+  <si>
+    <t>Francesca Carella</t>
+  </si>
+  <si>
+    <t>Barbara Valle</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1209,6 +1254,13 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1772,8 +1824,10 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="8" t="s">
+      <c r="Z2" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA2" s="31" t="s">
         <v>40</v>
       </c>
       <c r="AB2" s="8" t="s">
@@ -1845,8 +1899,10 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="8" t="s">
+      <c r="Z3" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA3" s="31" t="s">
         <v>50</v>
       </c>
       <c r="AB3" s="8" t="s">
@@ -1918,8 +1974,10 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="8" t="s">
+      <c r="Z4" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="AA4" s="31" t="s">
         <v>61</v>
       </c>
       <c r="AB4" s="8" t="s">
@@ -1991,8 +2049,10 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="8" t="s">
+      <c r="Z5" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="AA5" s="31" t="s">
         <v>70</v>
       </c>
       <c r="AB5" s="8" t="s">
@@ -2066,8 +2126,10 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="4" t="s">
+      <c r="Z6" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="AA6" s="29" t="s">
         <v>79</v>
       </c>
       <c r="AB6" s="4" t="s">
@@ -2141,8 +2203,10 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3" t="s">
+      <c r="Z7" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="AA7" s="32" t="s">
         <v>79</v>
       </c>
       <c r="AB7" s="3" t="s">
@@ -2214,8 +2278,10 @@
       <c r="W8" s="26"/>
       <c r="X8" s="26"/>
       <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="8" t="s">
+      <c r="Z8" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA8" s="31" t="s">
         <v>98</v>
       </c>
       <c r="AB8" s="8" t="s">
@@ -2285,8 +2351,10 @@
       <c r="W9" s="26"/>
       <c r="X9" s="26"/>
       <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="8" t="s">
+      <c r="Z9" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="AA9" s="31" t="s">
         <v>106</v>
       </c>
       <c r="AB9" s="8" t="s">
@@ -2358,8 +2426,10 @@
       <c r="W10" s="26"/>
       <c r="X10" s="26"/>
       <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="8" t="s">
+      <c r="Z10" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA10" s="31" t="s">
         <v>116</v>
       </c>
       <c r="AB10" s="8" t="s">
@@ -2431,8 +2501,10 @@
       <c r="W11" s="26"/>
       <c r="X11" s="26"/>
       <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="8" t="s">
+      <c r="Z11" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="AA11" s="31" t="s">
         <v>126</v>
       </c>
       <c r="AB11" s="8" t="s">
@@ -2504,8 +2576,10 @@
       <c r="W12" s="27"/>
       <c r="X12" s="27"/>
       <c r="Y12" s="12"/>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="15" t="s">
+      <c r="Z12" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="AA12" s="33" t="s">
         <v>136</v>
       </c>
       <c r="AB12" s="15" t="s">
@@ -2577,8 +2651,10 @@
       <c r="W13" s="26"/>
       <c r="X13" s="26"/>
       <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="16" t="s">
+      <c r="Z13" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="AA13" s="33" t="s">
         <v>146</v>
       </c>
       <c r="AB13" s="16" t="s">
@@ -2650,8 +2726,10 @@
       <c r="W14" s="26"/>
       <c r="X14" s="26"/>
       <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="16" t="s">
+      <c r="Z14" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="AA14" s="33" t="s">
         <v>156</v>
       </c>
       <c r="AB14" s="16" t="s">
@@ -2727,8 +2805,10 @@
         <v>233</v>
       </c>
       <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="16" t="s">
+      <c r="Z15" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA15" s="33" t="s">
         <v>165</v>
       </c>
       <c r="AB15" s="16" t="s">
@@ -2804,8 +2884,10 @@
         <v>234</v>
       </c>
       <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="16" t="s">
+      <c r="Z16" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA16" s="33" t="s">
         <v>165</v>
       </c>
       <c r="AB16" s="16" t="s">
@@ -2881,8 +2963,10 @@
         <v>235</v>
       </c>
       <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="16" t="s">
+      <c r="Z17" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA17" s="33" t="s">
         <v>165</v>
       </c>
       <c r="AB17" s="16" t="s">
@@ -2954,8 +3038,10 @@
       <c r="W18" s="26"/>
       <c r="X18" s="26"/>
       <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="8" t="s">
+      <c r="Z18" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA18" s="31" t="s">
         <v>189</v>
       </c>
       <c r="AB18" s="8" t="s">
@@ -3031,8 +3117,10 @@
         <v>238</v>
       </c>
       <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="16" t="s">
+      <c r="Z19" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="AA19" s="33" t="s">
         <v>197</v>
       </c>
       <c r="AB19" s="16" t="s">
